--- a/templates/SALES_ONBUY_TEMPLATE.xlsx
+++ b/templates/SALES_ONBUY_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -98,22 +98,19 @@
     <t>Colour</t>
   </si>
   <si>
-    <t>ONBUY-EXAMPLE</t>
+    <t>OB-9002</t>
   </si>
   <si>
-    <t>ASI-SG-S20-128-CG</t>
+    <t>PIX7-128-BLK</t>
   </si>
   <si>
-    <t>350100000000001</t>
+    <t>350100000031676</t>
   </si>
   <si>
-    <t>EXAMPLE SUPPLIER</t>
+    <t>NORTHSIDE STOCK</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>Samsung Galaxy S20 128GB</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -580,7 +577,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
         <v>32</v>
@@ -588,66 +585,66 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -764,10 +761,10 @@
         <v>31</v>
       </c>
       <c r="F2" s="3">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="G2" s="3">
-        <v>159.99</v>
+        <v>359</v>
       </c>
       <c r="H2" s="3">
         <f>IF($G2="","",G2-F2)</f>
@@ -782,7 +779,7 @@
         <f>IF($G2="","",J2*20%)</f>
       </c>
       <c r="L2" s="3">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M2" s="3">
         <f>IF($G2="","",L2*20%)</f>
@@ -806,7 +803,7 @@
         <v>32</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="3">
         <f>IF($G2="","",P2-Y2)</f>
@@ -8820,7 +8817,7 @@
     </row>
     <row r="203" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>

--- a/templates/SALES_ONBUY_TEMPLATE.xlsx
+++ b/templates/SALES_ONBUY_TEMPLATE.xlsx
@@ -767,37 +767,37 @@
         <v>359</v>
       </c>
       <c r="H2" s="3">
-        <f>IF($G2="","",G2-F2)</f>
+        <f>G2-F2</f>
       </c>
       <c r="I2" s="3">
-        <f>IF($G2="","",H2*16.67%)</f>
+        <f>H2*16.67%</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($G2="","",G2*7%)</f>
+        <f>G2*7%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($G2="","",J2*20%)</f>
+        <f>J2*20%</f>
       </c>
       <c r="L2" s="3">
         <v>8</v>
       </c>
       <c r="M2" s="3">
-        <f>IF($G2="","",L2*20%)</f>
+        <f>L2*20%</f>
       </c>
       <c r="N2" s="3">
         <v>1</v>
       </c>
       <c r="O2" s="3">
-        <f>IF($G2="","",K2+M2)</f>
+        <f>K2+M2</f>
       </c>
       <c r="P2" s="3">
-        <f>IF($G2="","",H2-I2-J2-K2-L2-M2-N2)</f>
+        <f>H2-I2-J2-K2-L2-M2-N2</f>
       </c>
       <c r="Q2" s="3">
-        <f>IF($G2="","",(P2-Y2)/F2*100)</f>
+        <f>(P2-Y2)/F2*100</f>
       </c>
       <c r="R2" s="3">
-        <f>IF($G2="","",I2-O2)</f>
+        <f>I2-O2</f>
       </c>
       <c r="S2" t="s">
         <v>32</v>
@@ -806,7 +806,7 @@
         <v>29</v>
       </c>
       <c r="Z2" s="3">
-        <f>IF($G2="","",P2-Y2)</f>
+        <f>P2-Y2</f>
       </c>
       <c r="AA2" t="s">
         <v>32</v>
@@ -815,7 +815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="F3" s="3"/>
@@ -855,7 +855,7 @@
         <f>IF($G3="","",P3-Y3)</f>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="F4" s="3"/>
@@ -895,7 +895,7 @@
         <f>IF($G4="","",P4-Y4)</f>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="F5" s="3"/>
@@ -935,7 +935,7 @@
         <f>IF($G5="","",P5-Y5)</f>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="F6" s="3"/>
@@ -975,7 +975,7 @@
         <f>IF($G6="","",P6-Y6)</f>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="F7" s="3"/>
@@ -1015,7 +1015,7 @@
         <f>IF($G7="","",P7-Y7)</f>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="F8" s="3"/>
@@ -1055,7 +1055,7 @@
         <f>IF($G8="","",P8-Y8)</f>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="F9" s="3"/>
@@ -1095,7 +1095,7 @@
         <f>IF($G9="","",P9-Y9)</f>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="F10" s="3"/>
@@ -1135,7 +1135,7 @@
         <f>IF($G10="","",P10-Y10)</f>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="F11" s="3"/>
@@ -1175,7 +1175,7 @@
         <f>IF($G11="","",P11-Y11)</f>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="F12" s="3"/>
@@ -1215,7 +1215,7 @@
         <f>IF($G12="","",P12-Y12)</f>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="F13" s="3"/>
@@ -1255,7 +1255,7 @@
         <f>IF($G13="","",P13-Y13)</f>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="F14" s="3"/>
@@ -1295,7 +1295,7 @@
         <f>IF($G14="","",P14-Y14)</f>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="F15" s="3"/>
@@ -1335,7 +1335,7 @@
         <f>IF($G15="","",P15-Y15)</f>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="F16" s="3"/>
@@ -1375,7 +1375,7 @@
         <f>IF($G16="","",P16-Y16)</f>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="F17" s="3"/>
@@ -1415,7 +1415,7 @@
         <f>IF($G17="","",P17-Y17)</f>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="F18" s="3"/>
@@ -1455,7 +1455,7 @@
         <f>IF($G18="","",P18-Y18)</f>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="F19" s="3"/>
@@ -1495,7 +1495,7 @@
         <f>IF($G19="","",P19-Y19)</f>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="F20" s="3"/>
@@ -1535,7 +1535,7 @@
         <f>IF($G20="","",P20-Y20)</f>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="F21" s="3"/>
@@ -1575,7 +1575,7 @@
         <f>IF($G21="","",P21-Y21)</f>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="F22" s="3"/>
@@ -1615,7 +1615,7 @@
         <f>IF($G22="","",P22-Y22)</f>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="F23" s="3"/>
@@ -1655,7 +1655,7 @@
         <f>IF($G23="","",P23-Y23)</f>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="F24" s="3"/>
@@ -1695,7 +1695,7 @@
         <f>IF($G24="","",P24-Y24)</f>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="F25" s="3"/>
@@ -1735,7 +1735,7 @@
         <f>IF($G25="","",P25-Y25)</f>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="F26" s="3"/>
@@ -1775,7 +1775,7 @@
         <f>IF($G26="","",P26-Y26)</f>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="F27" s="3"/>
@@ -1815,7 +1815,7 @@
         <f>IF($G27="","",P27-Y27)</f>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="F28" s="3"/>
@@ -1855,7 +1855,7 @@
         <f>IF($G28="","",P28-Y28)</f>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="F29" s="3"/>
@@ -1895,7 +1895,7 @@
         <f>IF($G29="","",P29-Y29)</f>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="F30" s="3"/>
@@ -1935,7 +1935,7 @@
         <f>IF($G30="","",P30-Y30)</f>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="F31" s="3"/>
@@ -1975,7 +1975,7 @@
         <f>IF($G31="","",P31-Y31)</f>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="F32" s="3"/>
@@ -2015,7 +2015,7 @@
         <f>IF($G32="","",P32-Y32)</f>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="F33" s="3"/>
@@ -2055,7 +2055,7 @@
         <f>IF($G33="","",P33-Y33)</f>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="F34" s="3"/>
@@ -2095,7 +2095,7 @@
         <f>IF($G34="","",P34-Y34)</f>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="F35" s="3"/>
@@ -2135,7 +2135,7 @@
         <f>IF($G35="","",P35-Y35)</f>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="F36" s="3"/>
@@ -2175,7 +2175,7 @@
         <f>IF($G36="","",P36-Y36)</f>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="F37" s="3"/>
@@ -2215,7 +2215,7 @@
         <f>IF($G37="","",P37-Y37)</f>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="F38" s="3"/>
@@ -2255,7 +2255,7 @@
         <f>IF($G38="","",P38-Y38)</f>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="F39" s="3"/>
@@ -2295,7 +2295,7 @@
         <f>IF($G39="","",P39-Y39)</f>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="F40" s="3"/>
@@ -2335,7 +2335,7 @@
         <f>IF($G40="","",P40-Y40)</f>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="F41" s="3"/>
@@ -2375,7 +2375,7 @@
         <f>IF($G41="","",P41-Y41)</f>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="F42" s="3"/>
@@ -2415,7 +2415,7 @@
         <f>IF($G42="","",P42-Y42)</f>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="F43" s="3"/>
@@ -2455,7 +2455,7 @@
         <f>IF($G43="","",P43-Y43)</f>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="F44" s="3"/>
@@ -2495,7 +2495,7 @@
         <f>IF($G44="","",P44-Y44)</f>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="F45" s="3"/>
@@ -2535,7 +2535,7 @@
         <f>IF($G45="","",P45-Y45)</f>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="F46" s="3"/>
@@ -2575,7 +2575,7 @@
         <f>IF($G46="","",P46-Y46)</f>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="F47" s="3"/>
@@ -2615,7 +2615,7 @@
         <f>IF($G47="","",P47-Y47)</f>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="F48" s="3"/>
@@ -2655,7 +2655,7 @@
         <f>IF($G48="","",P48-Y48)</f>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="F49" s="3"/>
@@ -2695,7 +2695,7 @@
         <f>IF($G49="","",P49-Y49)</f>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="F50" s="3"/>
@@ -2735,7 +2735,7 @@
         <f>IF($G50="","",P50-Y50)</f>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="F51" s="3"/>
@@ -2775,7 +2775,7 @@
         <f>IF($G51="","",P51-Y51)</f>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="F52" s="3"/>
@@ -2815,7 +2815,7 @@
         <f>IF($G52="","",P52-Y52)</f>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="F53" s="3"/>
@@ -2855,7 +2855,7 @@
         <f>IF($G53="","",P53-Y53)</f>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="F54" s="3"/>
@@ -2895,7 +2895,7 @@
         <f>IF($G54="","",P54-Y54)</f>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="F55" s="3"/>
@@ -2935,7 +2935,7 @@
         <f>IF($G55="","",P55-Y55)</f>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="F56" s="3"/>
@@ -2975,7 +2975,7 @@
         <f>IF($G56="","",P56-Y56)</f>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="F57" s="3"/>
@@ -3015,7 +3015,7 @@
         <f>IF($G57="","",P57-Y57)</f>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="F58" s="3"/>
@@ -3055,7 +3055,7 @@
         <f>IF($G58="","",P58-Y58)</f>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="F59" s="3"/>
@@ -3095,7 +3095,7 @@
         <f>IF($G59="","",P59-Y59)</f>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="F60" s="3"/>
@@ -3135,7 +3135,7 @@
         <f>IF($G60="","",P60-Y60)</f>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="F61" s="3"/>
@@ -3175,7 +3175,7 @@
         <f>IF($G61="","",P61-Y61)</f>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="F62" s="3"/>
@@ -3215,7 +3215,7 @@
         <f>IF($G62="","",P62-Y62)</f>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="F63" s="3"/>
@@ -3255,7 +3255,7 @@
         <f>IF($G63="","",P63-Y63)</f>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="F64" s="3"/>
@@ -3295,7 +3295,7 @@
         <f>IF($G64="","",P64-Y64)</f>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="F65" s="3"/>
@@ -3335,7 +3335,7 @@
         <f>IF($G65="","",P65-Y65)</f>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="F66" s="3"/>
@@ -3375,7 +3375,7 @@
         <f>IF($G66="","",P66-Y66)</f>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="F67" s="3"/>
@@ -3415,7 +3415,7 @@
         <f>IF($G67="","",P67-Y67)</f>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="F68" s="3"/>
@@ -3455,7 +3455,7 @@
         <f>IF($G68="","",P68-Y68)</f>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="F69" s="3"/>
@@ -3495,7 +3495,7 @@
         <f>IF($G69="","",P69-Y69)</f>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="F70" s="3"/>
@@ -3535,7 +3535,7 @@
         <f>IF($G70="","",P70-Y70)</f>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="F71" s="3"/>
@@ -3575,7 +3575,7 @@
         <f>IF($G71="","",P71-Y71)</f>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="F72" s="3"/>
@@ -3615,7 +3615,7 @@
         <f>IF($G72="","",P72-Y72)</f>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="F73" s="3"/>
@@ -3655,7 +3655,7 @@
         <f>IF($G73="","",P73-Y73)</f>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="F74" s="3"/>
@@ -3695,7 +3695,7 @@
         <f>IF($G74="","",P74-Y74)</f>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="F75" s="3"/>
@@ -3735,7 +3735,7 @@
         <f>IF($G75="","",P75-Y75)</f>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="F76" s="3"/>
@@ -3775,7 +3775,7 @@
         <f>IF($G76="","",P76-Y76)</f>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="F77" s="3"/>
@@ -3815,7 +3815,7 @@
         <f>IF($G77="","",P77-Y77)</f>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="F78" s="3"/>
@@ -3855,7 +3855,7 @@
         <f>IF($G78="","",P78-Y78)</f>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="F79" s="3"/>
@@ -3895,7 +3895,7 @@
         <f>IF($G79="","",P79-Y79)</f>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="F80" s="3"/>
@@ -3935,7 +3935,7 @@
         <f>IF($G80="","",P80-Y80)</f>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="F81" s="3"/>
@@ -3975,7 +3975,7 @@
         <f>IF($G81="","",P81-Y81)</f>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="F82" s="3"/>
@@ -4015,7 +4015,7 @@
         <f>IF($G82="","",P82-Y82)</f>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="F83" s="3"/>
@@ -4055,7 +4055,7 @@
         <f>IF($G83="","",P83-Y83)</f>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="F84" s="3"/>
@@ -4095,7 +4095,7 @@
         <f>IF($G84="","",P84-Y84)</f>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="F85" s="3"/>
@@ -4135,7 +4135,7 @@
         <f>IF($G85="","",P85-Y85)</f>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="F86" s="3"/>
@@ -4175,7 +4175,7 @@
         <f>IF($G86="","",P86-Y86)</f>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="F87" s="3"/>
@@ -4215,7 +4215,7 @@
         <f>IF($G87="","",P87-Y87)</f>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="F88" s="3"/>
@@ -4255,7 +4255,7 @@
         <f>IF($G88="","",P88-Y88)</f>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="F89" s="3"/>
@@ -4295,7 +4295,7 @@
         <f>IF($G89="","",P89-Y89)</f>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="F90" s="3"/>
@@ -4335,7 +4335,7 @@
         <f>IF($G90="","",P90-Y90)</f>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="F91" s="3"/>
@@ -4375,7 +4375,7 @@
         <f>IF($G91="","",P91-Y91)</f>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="F92" s="3"/>
@@ -4415,7 +4415,7 @@
         <f>IF($G92="","",P92-Y92)</f>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="F93" s="3"/>
@@ -4455,7 +4455,7 @@
         <f>IF($G93="","",P93-Y93)</f>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="F94" s="3"/>
@@ -4495,7 +4495,7 @@
         <f>IF($G94="","",P94-Y94)</f>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="F95" s="3"/>
@@ -4535,7 +4535,7 @@
         <f>IF($G95="","",P95-Y95)</f>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="F96" s="3"/>
@@ -4575,7 +4575,7 @@
         <f>IF($G96="","",P96-Y96)</f>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="F97" s="3"/>
@@ -4615,7 +4615,7 @@
         <f>IF($G97="","",P97-Y97)</f>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="F98" s="3"/>
@@ -4655,7 +4655,7 @@
         <f>IF($G98="","",P98-Y98)</f>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="F99" s="3"/>
@@ -4695,7 +4695,7 @@
         <f>IF($G99="","",P99-Y99)</f>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="F100" s="3"/>
@@ -4735,7 +4735,7 @@
         <f>IF($G100="","",P100-Y100)</f>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="F101" s="3"/>
@@ -4775,7 +4775,7 @@
         <f>IF($G101="","",P101-Y101)</f>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="F102" s="3"/>
@@ -4815,7 +4815,7 @@
         <f>IF($G102="","",P102-Y102)</f>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="F103" s="3"/>
@@ -4855,7 +4855,7 @@
         <f>IF($G103="","",P103-Y103)</f>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="F104" s="3"/>
@@ -4895,7 +4895,7 @@
         <f>IF($G104="","",P104-Y104)</f>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="F105" s="3"/>
@@ -4935,7 +4935,7 @@
         <f>IF($G105="","",P105-Y105)</f>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="F106" s="3"/>
@@ -4975,7 +4975,7 @@
         <f>IF($G106="","",P106-Y106)</f>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="F107" s="3"/>
@@ -5015,7 +5015,7 @@
         <f>IF($G107="","",P107-Y107)</f>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="F108" s="3"/>
@@ -5055,7 +5055,7 @@
         <f>IF($G108="","",P108-Y108)</f>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="F109" s="3"/>
@@ -5095,7 +5095,7 @@
         <f>IF($G109="","",P109-Y109)</f>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="F110" s="3"/>
@@ -5135,7 +5135,7 @@
         <f>IF($G110="","",P110-Y110)</f>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="F111" s="3"/>
@@ -5175,7 +5175,7 @@
         <f>IF($G111="","",P111-Y111)</f>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="F112" s="3"/>
@@ -5215,7 +5215,7 @@
         <f>IF($G112="","",P112-Y112)</f>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="F113" s="3"/>
@@ -5255,7 +5255,7 @@
         <f>IF($G113="","",P113-Y113)</f>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="F114" s="3"/>
@@ -5295,7 +5295,7 @@
         <f>IF($G114="","",P114-Y114)</f>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="F115" s="3"/>
@@ -5335,7 +5335,7 @@
         <f>IF($G115="","",P115-Y115)</f>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="F116" s="3"/>
@@ -5375,7 +5375,7 @@
         <f>IF($G116="","",P116-Y116)</f>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="F117" s="3"/>
@@ -5415,7 +5415,7 @@
         <f>IF($G117="","",P117-Y117)</f>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="F118" s="3"/>
@@ -5455,7 +5455,7 @@
         <f>IF($G118="","",P118-Y118)</f>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="F119" s="3"/>
@@ -5495,7 +5495,7 @@
         <f>IF($G119="","",P119-Y119)</f>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="F120" s="3"/>
@@ -5535,7 +5535,7 @@
         <f>IF($G120="","",P120-Y120)</f>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="F121" s="3"/>
@@ -5575,7 +5575,7 @@
         <f>IF($G121="","",P121-Y121)</f>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="F122" s="3"/>
@@ -5615,7 +5615,7 @@
         <f>IF($G122="","",P122-Y122)</f>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="F123" s="3"/>
@@ -5655,7 +5655,7 @@
         <f>IF($G123="","",P123-Y123)</f>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="F124" s="3"/>
@@ -5695,7 +5695,7 @@
         <f>IF($G124="","",P124-Y124)</f>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="F125" s="3"/>
@@ -5735,7 +5735,7 @@
         <f>IF($G125="","",P125-Y125)</f>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="F126" s="3"/>
@@ -5775,7 +5775,7 @@
         <f>IF($G126="","",P126-Y126)</f>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="F127" s="3"/>
@@ -5815,7 +5815,7 @@
         <f>IF($G127="","",P127-Y127)</f>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="F128" s="3"/>
@@ -5855,7 +5855,7 @@
         <f>IF($G128="","",P128-Y128)</f>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="F129" s="3"/>
@@ -5895,7 +5895,7 @@
         <f>IF($G129="","",P129-Y129)</f>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="F130" s="3"/>
@@ -5935,7 +5935,7 @@
         <f>IF($G130="","",P130-Y130)</f>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="F131" s="3"/>
@@ -5975,7 +5975,7 @@
         <f>IF($G131="","",P131-Y131)</f>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="F132" s="3"/>
@@ -6015,7 +6015,7 @@
         <f>IF($G132="","",P132-Y132)</f>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="F133" s="3"/>
@@ -6055,7 +6055,7 @@
         <f>IF($G133="","",P133-Y133)</f>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="F134" s="3"/>
@@ -6095,7 +6095,7 @@
         <f>IF($G134="","",P134-Y134)</f>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="F135" s="3"/>
@@ -6135,7 +6135,7 @@
         <f>IF($G135="","",P135-Y135)</f>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="F136" s="3"/>
@@ -6175,7 +6175,7 @@
         <f>IF($G136="","",P136-Y136)</f>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="F137" s="3"/>
@@ -6215,7 +6215,7 @@
         <f>IF($G137="","",P137-Y137)</f>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="F138" s="3"/>
@@ -6255,7 +6255,7 @@
         <f>IF($G138="","",P138-Y138)</f>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="F139" s="3"/>
@@ -6295,7 +6295,7 @@
         <f>IF($G139="","",P139-Y139)</f>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="F140" s="3"/>
@@ -6335,7 +6335,7 @@
         <f>IF($G140="","",P140-Y140)</f>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="F141" s="3"/>
@@ -6375,7 +6375,7 @@
         <f>IF($G141="","",P141-Y141)</f>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="F142" s="3"/>
@@ -6415,7 +6415,7 @@
         <f>IF($G142="","",P142-Y142)</f>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="F143" s="3"/>
@@ -6455,7 +6455,7 @@
         <f>IF($G143="","",P143-Y143)</f>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="F144" s="3"/>
@@ -6495,7 +6495,7 @@
         <f>IF($G144="","",P144-Y144)</f>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="F145" s="3"/>
@@ -6535,7 +6535,7 @@
         <f>IF($G145="","",P145-Y145)</f>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="F146" s="3"/>
@@ -6575,7 +6575,7 @@
         <f>IF($G146="","",P146-Y146)</f>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="F147" s="3"/>
@@ -6615,7 +6615,7 @@
         <f>IF($G147="","",P147-Y147)</f>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="F148" s="3"/>
@@ -6655,7 +6655,7 @@
         <f>IF($G148="","",P148-Y148)</f>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="F149" s="3"/>
@@ -6695,7 +6695,7 @@
         <f>IF($G149="","",P149-Y149)</f>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="F150" s="3"/>
@@ -6735,7 +6735,7 @@
         <f>IF($G150="","",P150-Y150)</f>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="F151" s="3"/>
@@ -6775,7 +6775,7 @@
         <f>IF($G151="","",P151-Y151)</f>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="F152" s="3"/>
@@ -6815,7 +6815,7 @@
         <f>IF($G152="","",P152-Y152)</f>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="F153" s="3"/>
@@ -6855,7 +6855,7 @@
         <f>IF($G153="","",P153-Y153)</f>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="F154" s="3"/>
@@ -6895,7 +6895,7 @@
         <f>IF($G154="","",P154-Y154)</f>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="F155" s="3"/>
@@ -6935,7 +6935,7 @@
         <f>IF($G155="","",P155-Y155)</f>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="F156" s="3"/>
@@ -6975,7 +6975,7 @@
         <f>IF($G156="","",P156-Y156)</f>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="F157" s="3"/>
@@ -7015,7 +7015,7 @@
         <f>IF($G157="","",P157-Y157)</f>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="F158" s="3"/>
@@ -7055,7 +7055,7 @@
         <f>IF($G158="","",P158-Y158)</f>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="F159" s="3"/>
@@ -7095,7 +7095,7 @@
         <f>IF($G159="","",P159-Y159)</f>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="F160" s="3"/>
@@ -7135,7 +7135,7 @@
         <f>IF($G160="","",P160-Y160)</f>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="F161" s="3"/>
@@ -7175,7 +7175,7 @@
         <f>IF($G161="","",P161-Y161)</f>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="F162" s="3"/>
@@ -7215,7 +7215,7 @@
         <f>IF($G162="","",P162-Y162)</f>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="F163" s="3"/>
@@ -7255,7 +7255,7 @@
         <f>IF($G163="","",P163-Y163)</f>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="F164" s="3"/>
@@ -7295,7 +7295,7 @@
         <f>IF($G164="","",P164-Y164)</f>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="F165" s="3"/>
@@ -7335,7 +7335,7 @@
         <f>IF($G165="","",P165-Y165)</f>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="F166" s="3"/>
@@ -7375,7 +7375,7 @@
         <f>IF($G166="","",P166-Y166)</f>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="F167" s="3"/>
@@ -7415,7 +7415,7 @@
         <f>IF($G167="","",P167-Y167)</f>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="F168" s="3"/>
@@ -7455,7 +7455,7 @@
         <f>IF($G168="","",P168-Y168)</f>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="F169" s="3"/>
@@ -7495,7 +7495,7 @@
         <f>IF($G169="","",P169-Y169)</f>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="F170" s="3"/>
@@ -7535,7 +7535,7 @@
         <f>IF($G170="","",P170-Y170)</f>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="F171" s="3"/>
@@ -7575,7 +7575,7 @@
         <f>IF($G171="","",P171-Y171)</f>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="F172" s="3"/>
@@ -7615,7 +7615,7 @@
         <f>IF($G172="","",P172-Y172)</f>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="F173" s="3"/>
@@ -7655,7 +7655,7 @@
         <f>IF($G173="","",P173-Y173)</f>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="F174" s="3"/>
@@ -7695,7 +7695,7 @@
         <f>IF($G174="","",P174-Y174)</f>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="F175" s="3"/>
@@ -7735,7 +7735,7 @@
         <f>IF($G175="","",P175-Y175)</f>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="F176" s="3"/>
@@ -7775,7 +7775,7 @@
         <f>IF($G176="","",P176-Y176)</f>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="F177" s="3"/>
@@ -7815,7 +7815,7 @@
         <f>IF($G177="","",P177-Y177)</f>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="F178" s="3"/>
@@ -7855,7 +7855,7 @@
         <f>IF($G178="","",P178-Y178)</f>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="F179" s="3"/>
@@ -7895,7 +7895,7 @@
         <f>IF($G179="","",P179-Y179)</f>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="F180" s="3"/>
@@ -7935,7 +7935,7 @@
         <f>IF($G180="","",P180-Y180)</f>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="F181" s="3"/>
@@ -7975,7 +7975,7 @@
         <f>IF($G181="","",P181-Y181)</f>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="F182" s="3"/>
@@ -8015,7 +8015,7 @@
         <f>IF($G182="","",P182-Y182)</f>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="F183" s="3"/>
@@ -8055,7 +8055,7 @@
         <f>IF($G183="","",P183-Y183)</f>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="F184" s="3"/>
@@ -8095,7 +8095,7 @@
         <f>IF($G184="","",P184-Y184)</f>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="F185" s="3"/>
@@ -8135,7 +8135,7 @@
         <f>IF($G185="","",P185-Y185)</f>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="F186" s="3"/>
@@ -8175,7 +8175,7 @@
         <f>IF($G186="","",P186-Y186)</f>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="F187" s="3"/>
@@ -8215,7 +8215,7 @@
         <f>IF($G187="","",P187-Y187)</f>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="F188" s="3"/>
@@ -8255,7 +8255,7 @@
         <f>IF($G188="","",P188-Y188)</f>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="F189" s="3"/>
@@ -8295,7 +8295,7 @@
         <f>IF($G189="","",P189-Y189)</f>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="F190" s="3"/>
@@ -8335,7 +8335,7 @@
         <f>IF($G190="","",P190-Y190)</f>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="F191" s="3"/>
@@ -8375,7 +8375,7 @@
         <f>IF($G191="","",P191-Y191)</f>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="F192" s="3"/>
@@ -8415,7 +8415,7 @@
         <f>IF($G192="","",P192-Y192)</f>
       </c>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="F193" s="3"/>
@@ -8455,7 +8455,7 @@
         <f>IF($G193="","",P193-Y193)</f>
       </c>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="F194" s="3"/>
@@ -8495,7 +8495,7 @@
         <f>IF($G194="","",P194-Y194)</f>
       </c>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="F195" s="3"/>
@@ -8535,7 +8535,7 @@
         <f>IF($G195="","",P195-Y195)</f>
       </c>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="F196" s="3"/>
@@ -8575,7 +8575,7 @@
         <f>IF($G196="","",P196-Y196)</f>
       </c>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="F197" s="3"/>
@@ -8615,7 +8615,7 @@
         <f>IF($G197="","",P197-Y197)</f>
       </c>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="F198" s="3"/>
@@ -8655,7 +8655,7 @@
         <f>IF($G198="","",P198-Y198)</f>
       </c>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="F199" s="3"/>
@@ -8695,7 +8695,7 @@
         <f>IF($G199="","",P199-Y199)</f>
       </c>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="F200" s="3"/>
@@ -8735,7 +8735,7 @@
         <f>IF($G200="","",P200-Y200)</f>
       </c>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="F201" s="3"/>
@@ -8775,7 +8775,7 @@
         <f>IF($G201="","",P201-Y201)</f>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="F202" s="3"/>

--- a/templates/SALES_ONBUY_TEMPLATE.xlsx
+++ b/templates/SALES_ONBUY_TEMPLATE.xlsx
@@ -62,7 +62,7 @@
     <t>P. VAT</t>
   </si>
   <si>
-    <t>Accessories</t>
+    <t>Acc</t>
   </si>
   <si>
     <t>Total VAT</t>

--- a/templates/SALES_ONBUY_TEMPLATE.xlsx
+++ b/templates/SALES_ONBUY_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -577,74 +589,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -655,10 +667,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB203"/>
+  <dimension ref="A1:AF203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -743,31 +755,43 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I2" s="3">
         <v>275</v>
@@ -803,19 +827,19 @@
         <f>K2-L2-M2-N2-O2-P2-Q2</f>
       </c>
       <c r="T2" s="3">
-        <f>(S2-V2)/I2*100</f>
+        <f>(S2-Z2)/I2*100</f>
       </c>
       <c r="U2" s="3">
         <f>L2-R2</f>
       </c>
-      <c r="W2" s="3">
-        <f>S2-V2</f>
-      </c>
-      <c r="AB2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA2" s="3">
+        <f>S2-Z2</f>
+      </c>
+      <c r="AF2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="I3" s="3"/>
@@ -846,16 +870,16 @@
         <f>IF($J3="","",K3-L3-M3-N3-O3-P3-Q3)</f>
       </c>
       <c r="T3" s="3">
-        <f>IF($J3="","",(S3-V3)/I3*100)</f>
+        <f>IF($J3="","",(S3-Z3)/I3*100)</f>
       </c>
       <c r="U3" s="3">
         <f>IF($J3="","",L3-R3)</f>
       </c>
-      <c r="W3" s="3">
-        <f>IF($J3="","",S3-V3)</f>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA3" s="3">
+        <f>IF($J3="","",S3-Z3)</f>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="I4" s="3"/>
@@ -886,16 +910,16 @@
         <f>IF($J4="","",K4-L4-M4-N4-O4-P4-Q4)</f>
       </c>
       <c r="T4" s="3">
-        <f>IF($J4="","",(S4-V4)/I4*100)</f>
+        <f>IF($J4="","",(S4-Z4)/I4*100)</f>
       </c>
       <c r="U4" s="3">
         <f>IF($J4="","",L4-R4)</f>
       </c>
-      <c r="W4" s="3">
-        <f>IF($J4="","",S4-V4)</f>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA4" s="3">
+        <f>IF($J4="","",S4-Z4)</f>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="I5" s="3"/>
@@ -926,16 +950,16 @@
         <f>IF($J5="","",K5-L5-M5-N5-O5-P5-Q5)</f>
       </c>
       <c r="T5" s="3">
-        <f>IF($J5="","",(S5-V5)/I5*100)</f>
+        <f>IF($J5="","",(S5-Z5)/I5*100)</f>
       </c>
       <c r="U5" s="3">
         <f>IF($J5="","",L5-R5)</f>
       </c>
-      <c r="W5" s="3">
-        <f>IF($J5="","",S5-V5)</f>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA5" s="3">
+        <f>IF($J5="","",S5-Z5)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="I6" s="3"/>
@@ -966,16 +990,16 @@
         <f>IF($J6="","",K6-L6-M6-N6-O6-P6-Q6)</f>
       </c>
       <c r="T6" s="3">
-        <f>IF($J6="","",(S6-V6)/I6*100)</f>
+        <f>IF($J6="","",(S6-Z6)/I6*100)</f>
       </c>
       <c r="U6" s="3">
         <f>IF($J6="","",L6-R6)</f>
       </c>
-      <c r="W6" s="3">
-        <f>IF($J6="","",S6-V6)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA6" s="3">
+        <f>IF($J6="","",S6-Z6)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="I7" s="3"/>
@@ -1006,16 +1030,16 @@
         <f>IF($J7="","",K7-L7-M7-N7-O7-P7-Q7)</f>
       </c>
       <c r="T7" s="3">
-        <f>IF($J7="","",(S7-V7)/I7*100)</f>
+        <f>IF($J7="","",(S7-Z7)/I7*100)</f>
       </c>
       <c r="U7" s="3">
         <f>IF($J7="","",L7-R7)</f>
       </c>
-      <c r="W7" s="3">
-        <f>IF($J7="","",S7-V7)</f>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA7" s="3">
+        <f>IF($J7="","",S7-Z7)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="I8" s="3"/>
@@ -1046,16 +1070,16 @@
         <f>IF($J8="","",K8-L8-M8-N8-O8-P8-Q8)</f>
       </c>
       <c r="T8" s="3">
-        <f>IF($J8="","",(S8-V8)/I8*100)</f>
+        <f>IF($J8="","",(S8-Z8)/I8*100)</f>
       </c>
       <c r="U8" s="3">
         <f>IF($J8="","",L8-R8)</f>
       </c>
-      <c r="W8" s="3">
-        <f>IF($J8="","",S8-V8)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA8" s="3">
+        <f>IF($J8="","",S8-Z8)</f>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="I9" s="3"/>
@@ -1086,16 +1110,16 @@
         <f>IF($J9="","",K9-L9-M9-N9-O9-P9-Q9)</f>
       </c>
       <c r="T9" s="3">
-        <f>IF($J9="","",(S9-V9)/I9*100)</f>
+        <f>IF($J9="","",(S9-Z9)/I9*100)</f>
       </c>
       <c r="U9" s="3">
         <f>IF($J9="","",L9-R9)</f>
       </c>
-      <c r="W9" s="3">
-        <f>IF($J9="","",S9-V9)</f>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA9" s="3">
+        <f>IF($J9="","",S9-Z9)</f>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="I10" s="3"/>
@@ -1126,16 +1150,16 @@
         <f>IF($J10="","",K10-L10-M10-N10-O10-P10-Q10)</f>
       </c>
       <c r="T10" s="3">
-        <f>IF($J10="","",(S10-V10)/I10*100)</f>
+        <f>IF($J10="","",(S10-Z10)/I10*100)</f>
       </c>
       <c r="U10" s="3">
         <f>IF($J10="","",L10-R10)</f>
       </c>
-      <c r="W10" s="3">
-        <f>IF($J10="","",S10-V10)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA10" s="3">
+        <f>IF($J10="","",S10-Z10)</f>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="I11" s="3"/>
@@ -1166,16 +1190,16 @@
         <f>IF($J11="","",K11-L11-M11-N11-O11-P11-Q11)</f>
       </c>
       <c r="T11" s="3">
-        <f>IF($J11="","",(S11-V11)/I11*100)</f>
+        <f>IF($J11="","",(S11-Z11)/I11*100)</f>
       </c>
       <c r="U11" s="3">
         <f>IF($J11="","",L11-R11)</f>
       </c>
-      <c r="W11" s="3">
-        <f>IF($J11="","",S11-V11)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA11" s="3">
+        <f>IF($J11="","",S11-Z11)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="I12" s="3"/>
@@ -1206,16 +1230,16 @@
         <f>IF($J12="","",K12-L12-M12-N12-O12-P12-Q12)</f>
       </c>
       <c r="T12" s="3">
-        <f>IF($J12="","",(S12-V12)/I12*100)</f>
+        <f>IF($J12="","",(S12-Z12)/I12*100)</f>
       </c>
       <c r="U12" s="3">
         <f>IF($J12="","",L12-R12)</f>
       </c>
-      <c r="W12" s="3">
-        <f>IF($J12="","",S12-V12)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA12" s="3">
+        <f>IF($J12="","",S12-Z12)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="I13" s="3"/>
@@ -1246,16 +1270,16 @@
         <f>IF($J13="","",K13-L13-M13-N13-O13-P13-Q13)</f>
       </c>
       <c r="T13" s="3">
-        <f>IF($J13="","",(S13-V13)/I13*100)</f>
+        <f>IF($J13="","",(S13-Z13)/I13*100)</f>
       </c>
       <c r="U13" s="3">
         <f>IF($J13="","",L13-R13)</f>
       </c>
-      <c r="W13" s="3">
-        <f>IF($J13="","",S13-V13)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA13" s="3">
+        <f>IF($J13="","",S13-Z13)</f>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="I14" s="3"/>
@@ -1286,16 +1310,16 @@
         <f>IF($J14="","",K14-L14-M14-N14-O14-P14-Q14)</f>
       </c>
       <c r="T14" s="3">
-        <f>IF($J14="","",(S14-V14)/I14*100)</f>
+        <f>IF($J14="","",(S14-Z14)/I14*100)</f>
       </c>
       <c r="U14" s="3">
         <f>IF($J14="","",L14-R14)</f>
       </c>
-      <c r="W14" s="3">
-        <f>IF($J14="","",S14-V14)</f>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA14" s="3">
+        <f>IF($J14="","",S14-Z14)</f>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="I15" s="3"/>
@@ -1326,16 +1350,16 @@
         <f>IF($J15="","",K15-L15-M15-N15-O15-P15-Q15)</f>
       </c>
       <c r="T15" s="3">
-        <f>IF($J15="","",(S15-V15)/I15*100)</f>
+        <f>IF($J15="","",(S15-Z15)/I15*100)</f>
       </c>
       <c r="U15" s="3">
         <f>IF($J15="","",L15-R15)</f>
       </c>
-      <c r="W15" s="3">
-        <f>IF($J15="","",S15-V15)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA15" s="3">
+        <f>IF($J15="","",S15-Z15)</f>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="I16" s="3"/>
@@ -1366,16 +1390,16 @@
         <f>IF($J16="","",K16-L16-M16-N16-O16-P16-Q16)</f>
       </c>
       <c r="T16" s="3">
-        <f>IF($J16="","",(S16-V16)/I16*100)</f>
+        <f>IF($J16="","",(S16-Z16)/I16*100)</f>
       </c>
       <c r="U16" s="3">
         <f>IF($J16="","",L16-R16)</f>
       </c>
-      <c r="W16" s="3">
-        <f>IF($J16="","",S16-V16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA16" s="3">
+        <f>IF($J16="","",S16-Z16)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="I17" s="3"/>
@@ -1406,16 +1430,16 @@
         <f>IF($J17="","",K17-L17-M17-N17-O17-P17-Q17)</f>
       </c>
       <c r="T17" s="3">
-        <f>IF($J17="","",(S17-V17)/I17*100)</f>
+        <f>IF($J17="","",(S17-Z17)/I17*100)</f>
       </c>
       <c r="U17" s="3">
         <f>IF($J17="","",L17-R17)</f>
       </c>
-      <c r="W17" s="3">
-        <f>IF($J17="","",S17-V17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA17" s="3">
+        <f>IF($J17="","",S17-Z17)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="I18" s="3"/>
@@ -1446,16 +1470,16 @@
         <f>IF($J18="","",K18-L18-M18-N18-O18-P18-Q18)</f>
       </c>
       <c r="T18" s="3">
-        <f>IF($J18="","",(S18-V18)/I18*100)</f>
+        <f>IF($J18="","",(S18-Z18)/I18*100)</f>
       </c>
       <c r="U18" s="3">
         <f>IF($J18="","",L18-R18)</f>
       </c>
-      <c r="W18" s="3">
-        <f>IF($J18="","",S18-V18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA18" s="3">
+        <f>IF($J18="","",S18-Z18)</f>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="I19" s="3"/>
@@ -1486,16 +1510,16 @@
         <f>IF($J19="","",K19-L19-M19-N19-O19-P19-Q19)</f>
       </c>
       <c r="T19" s="3">
-        <f>IF($J19="","",(S19-V19)/I19*100)</f>
+        <f>IF($J19="","",(S19-Z19)/I19*100)</f>
       </c>
       <c r="U19" s="3">
         <f>IF($J19="","",L19-R19)</f>
       </c>
-      <c r="W19" s="3">
-        <f>IF($J19="","",S19-V19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA19" s="3">
+        <f>IF($J19="","",S19-Z19)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="I20" s="3"/>
@@ -1526,16 +1550,16 @@
         <f>IF($J20="","",K20-L20-M20-N20-O20-P20-Q20)</f>
       </c>
       <c r="T20" s="3">
-        <f>IF($J20="","",(S20-V20)/I20*100)</f>
+        <f>IF($J20="","",(S20-Z20)/I20*100)</f>
       </c>
       <c r="U20" s="3">
         <f>IF($J20="","",L20-R20)</f>
       </c>
-      <c r="W20" s="3">
-        <f>IF($J20="","",S20-V20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA20" s="3">
+        <f>IF($J20="","",S20-Z20)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="I21" s="3"/>
@@ -1566,16 +1590,16 @@
         <f>IF($J21="","",K21-L21-M21-N21-O21-P21-Q21)</f>
       </c>
       <c r="T21" s="3">
-        <f>IF($J21="","",(S21-V21)/I21*100)</f>
+        <f>IF($J21="","",(S21-Z21)/I21*100)</f>
       </c>
       <c r="U21" s="3">
         <f>IF($J21="","",L21-R21)</f>
       </c>
-      <c r="W21" s="3">
-        <f>IF($J21="","",S21-V21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA21" s="3">
+        <f>IF($J21="","",S21-Z21)</f>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="I22" s="3"/>
@@ -1606,16 +1630,16 @@
         <f>IF($J22="","",K22-L22-M22-N22-O22-P22-Q22)</f>
       </c>
       <c r="T22" s="3">
-        <f>IF($J22="","",(S22-V22)/I22*100)</f>
+        <f>IF($J22="","",(S22-Z22)/I22*100)</f>
       </c>
       <c r="U22" s="3">
         <f>IF($J22="","",L22-R22)</f>
       </c>
-      <c r="W22" s="3">
-        <f>IF($J22="","",S22-V22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA22" s="3">
+        <f>IF($J22="","",S22-Z22)</f>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="I23" s="3"/>
@@ -1646,16 +1670,16 @@
         <f>IF($J23="","",K23-L23-M23-N23-O23-P23-Q23)</f>
       </c>
       <c r="T23" s="3">
-        <f>IF($J23="","",(S23-V23)/I23*100)</f>
+        <f>IF($J23="","",(S23-Z23)/I23*100)</f>
       </c>
       <c r="U23" s="3">
         <f>IF($J23="","",L23-R23)</f>
       </c>
-      <c r="W23" s="3">
-        <f>IF($J23="","",S23-V23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA23" s="3">
+        <f>IF($J23="","",S23-Z23)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="I24" s="3"/>
@@ -1686,16 +1710,16 @@
         <f>IF($J24="","",K24-L24-M24-N24-O24-P24-Q24)</f>
       </c>
       <c r="T24" s="3">
-        <f>IF($J24="","",(S24-V24)/I24*100)</f>
+        <f>IF($J24="","",(S24-Z24)/I24*100)</f>
       </c>
       <c r="U24" s="3">
         <f>IF($J24="","",L24-R24)</f>
       </c>
-      <c r="W24" s="3">
-        <f>IF($J24="","",S24-V24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA24" s="3">
+        <f>IF($J24="","",S24-Z24)</f>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="I25" s="3"/>
@@ -1726,16 +1750,16 @@
         <f>IF($J25="","",K25-L25-M25-N25-O25-P25-Q25)</f>
       </c>
       <c r="T25" s="3">
-        <f>IF($J25="","",(S25-V25)/I25*100)</f>
+        <f>IF($J25="","",(S25-Z25)/I25*100)</f>
       </c>
       <c r="U25" s="3">
         <f>IF($J25="","",L25-R25)</f>
       </c>
-      <c r="W25" s="3">
-        <f>IF($J25="","",S25-V25)</f>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA25" s="3">
+        <f>IF($J25="","",S25-Z25)</f>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="I26" s="3"/>
@@ -1766,16 +1790,16 @@
         <f>IF($J26="","",K26-L26-M26-N26-O26-P26-Q26)</f>
       </c>
       <c r="T26" s="3">
-        <f>IF($J26="","",(S26-V26)/I26*100)</f>
+        <f>IF($J26="","",(S26-Z26)/I26*100)</f>
       </c>
       <c r="U26" s="3">
         <f>IF($J26="","",L26-R26)</f>
       </c>
-      <c r="W26" s="3">
-        <f>IF($J26="","",S26-V26)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA26" s="3">
+        <f>IF($J26="","",S26-Z26)</f>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="I27" s="3"/>
@@ -1806,16 +1830,16 @@
         <f>IF($J27="","",K27-L27-M27-N27-O27-P27-Q27)</f>
       </c>
       <c r="T27" s="3">
-        <f>IF($J27="","",(S27-V27)/I27*100)</f>
+        <f>IF($J27="","",(S27-Z27)/I27*100)</f>
       </c>
       <c r="U27" s="3">
         <f>IF($J27="","",L27-R27)</f>
       </c>
-      <c r="W27" s="3">
-        <f>IF($J27="","",S27-V27)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA27" s="3">
+        <f>IF($J27="","",S27-Z27)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="I28" s="3"/>
@@ -1846,16 +1870,16 @@
         <f>IF($J28="","",K28-L28-M28-N28-O28-P28-Q28)</f>
       </c>
       <c r="T28" s="3">
-        <f>IF($J28="","",(S28-V28)/I28*100)</f>
+        <f>IF($J28="","",(S28-Z28)/I28*100)</f>
       </c>
       <c r="U28" s="3">
         <f>IF($J28="","",L28-R28)</f>
       </c>
-      <c r="W28" s="3">
-        <f>IF($J28="","",S28-V28)</f>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA28" s="3">
+        <f>IF($J28="","",S28-Z28)</f>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="I29" s="3"/>
@@ -1886,16 +1910,16 @@
         <f>IF($J29="","",K29-L29-M29-N29-O29-P29-Q29)</f>
       </c>
       <c r="T29" s="3">
-        <f>IF($J29="","",(S29-V29)/I29*100)</f>
+        <f>IF($J29="","",(S29-Z29)/I29*100)</f>
       </c>
       <c r="U29" s="3">
         <f>IF($J29="","",L29-R29)</f>
       </c>
-      <c r="W29" s="3">
-        <f>IF($J29="","",S29-V29)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA29" s="3">
+        <f>IF($J29="","",S29-Z29)</f>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="I30" s="3"/>
@@ -1926,16 +1950,16 @@
         <f>IF($J30="","",K30-L30-M30-N30-O30-P30-Q30)</f>
       </c>
       <c r="T30" s="3">
-        <f>IF($J30="","",(S30-V30)/I30*100)</f>
+        <f>IF($J30="","",(S30-Z30)/I30*100)</f>
       </c>
       <c r="U30" s="3">
         <f>IF($J30="","",L30-R30)</f>
       </c>
-      <c r="W30" s="3">
-        <f>IF($J30="","",S30-V30)</f>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA30" s="3">
+        <f>IF($J30="","",S30-Z30)</f>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="I31" s="3"/>
@@ -1966,16 +1990,16 @@
         <f>IF($J31="","",K31-L31-M31-N31-O31-P31-Q31)</f>
       </c>
       <c r="T31" s="3">
-        <f>IF($J31="","",(S31-V31)/I31*100)</f>
+        <f>IF($J31="","",(S31-Z31)/I31*100)</f>
       </c>
       <c r="U31" s="3">
         <f>IF($J31="","",L31-R31)</f>
       </c>
-      <c r="W31" s="3">
-        <f>IF($J31="","",S31-V31)</f>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA31" s="3">
+        <f>IF($J31="","",S31-Z31)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="I32" s="3"/>
@@ -2006,16 +2030,16 @@
         <f>IF($J32="","",K32-L32-M32-N32-O32-P32-Q32)</f>
       </c>
       <c r="T32" s="3">
-        <f>IF($J32="","",(S32-V32)/I32*100)</f>
+        <f>IF($J32="","",(S32-Z32)/I32*100)</f>
       </c>
       <c r="U32" s="3">
         <f>IF($J32="","",L32-R32)</f>
       </c>
-      <c r="W32" s="3">
-        <f>IF($J32="","",S32-V32)</f>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA32" s="3">
+        <f>IF($J32="","",S32-Z32)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="I33" s="3"/>
@@ -2046,16 +2070,16 @@
         <f>IF($J33="","",K33-L33-M33-N33-O33-P33-Q33)</f>
       </c>
       <c r="T33" s="3">
-        <f>IF($J33="","",(S33-V33)/I33*100)</f>
+        <f>IF($J33="","",(S33-Z33)/I33*100)</f>
       </c>
       <c r="U33" s="3">
         <f>IF($J33="","",L33-R33)</f>
       </c>
-      <c r="W33" s="3">
-        <f>IF($J33="","",S33-V33)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA33" s="3">
+        <f>IF($J33="","",S33-Z33)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="I34" s="3"/>
@@ -2086,16 +2110,16 @@
         <f>IF($J34="","",K34-L34-M34-N34-O34-P34-Q34)</f>
       </c>
       <c r="T34" s="3">
-        <f>IF($J34="","",(S34-V34)/I34*100)</f>
+        <f>IF($J34="","",(S34-Z34)/I34*100)</f>
       </c>
       <c r="U34" s="3">
         <f>IF($J34="","",L34-R34)</f>
       </c>
-      <c r="W34" s="3">
-        <f>IF($J34="","",S34-V34)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA34" s="3">
+        <f>IF($J34="","",S34-Z34)</f>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="I35" s="3"/>
@@ -2126,16 +2150,16 @@
         <f>IF($J35="","",K35-L35-M35-N35-O35-P35-Q35)</f>
       </c>
       <c r="T35" s="3">
-        <f>IF($J35="","",(S35-V35)/I35*100)</f>
+        <f>IF($J35="","",(S35-Z35)/I35*100)</f>
       </c>
       <c r="U35" s="3">
         <f>IF($J35="","",L35-R35)</f>
       </c>
-      <c r="W35" s="3">
-        <f>IF($J35="","",S35-V35)</f>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA35" s="3">
+        <f>IF($J35="","",S35-Z35)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="I36" s="3"/>
@@ -2166,16 +2190,16 @@
         <f>IF($J36="","",K36-L36-M36-N36-O36-P36-Q36)</f>
       </c>
       <c r="T36" s="3">
-        <f>IF($J36="","",(S36-V36)/I36*100)</f>
+        <f>IF($J36="","",(S36-Z36)/I36*100)</f>
       </c>
       <c r="U36" s="3">
         <f>IF($J36="","",L36-R36)</f>
       </c>
-      <c r="W36" s="3">
-        <f>IF($J36="","",S36-V36)</f>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA36" s="3">
+        <f>IF($J36="","",S36-Z36)</f>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="I37" s="3"/>
@@ -2206,16 +2230,16 @@
         <f>IF($J37="","",K37-L37-M37-N37-O37-P37-Q37)</f>
       </c>
       <c r="T37" s="3">
-        <f>IF($J37="","",(S37-V37)/I37*100)</f>
+        <f>IF($J37="","",(S37-Z37)/I37*100)</f>
       </c>
       <c r="U37" s="3">
         <f>IF($J37="","",L37-R37)</f>
       </c>
-      <c r="W37" s="3">
-        <f>IF($J37="","",S37-V37)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA37" s="3">
+        <f>IF($J37="","",S37-Z37)</f>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="I38" s="3"/>
@@ -2246,16 +2270,16 @@
         <f>IF($J38="","",K38-L38-M38-N38-O38-P38-Q38)</f>
       </c>
       <c r="T38" s="3">
-        <f>IF($J38="","",(S38-V38)/I38*100)</f>
+        <f>IF($J38="","",(S38-Z38)/I38*100)</f>
       </c>
       <c r="U38" s="3">
         <f>IF($J38="","",L38-R38)</f>
       </c>
-      <c r="W38" s="3">
-        <f>IF($J38="","",S38-V38)</f>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA38" s="3">
+        <f>IF($J38="","",S38-Z38)</f>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="I39" s="3"/>
@@ -2286,16 +2310,16 @@
         <f>IF($J39="","",K39-L39-M39-N39-O39-P39-Q39)</f>
       </c>
       <c r="T39" s="3">
-        <f>IF($J39="","",(S39-V39)/I39*100)</f>
+        <f>IF($J39="","",(S39-Z39)/I39*100)</f>
       </c>
       <c r="U39" s="3">
         <f>IF($J39="","",L39-R39)</f>
       </c>
-      <c r="W39" s="3">
-        <f>IF($J39="","",S39-V39)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA39" s="3">
+        <f>IF($J39="","",S39-Z39)</f>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="I40" s="3"/>
@@ -2326,16 +2350,16 @@
         <f>IF($J40="","",K40-L40-M40-N40-O40-P40-Q40)</f>
       </c>
       <c r="T40" s="3">
-        <f>IF($J40="","",(S40-V40)/I40*100)</f>
+        <f>IF($J40="","",(S40-Z40)/I40*100)</f>
       </c>
       <c r="U40" s="3">
         <f>IF($J40="","",L40-R40)</f>
       </c>
-      <c r="W40" s="3">
-        <f>IF($J40="","",S40-V40)</f>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA40" s="3">
+        <f>IF($J40="","",S40-Z40)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="I41" s="3"/>
@@ -2366,16 +2390,16 @@
         <f>IF($J41="","",K41-L41-M41-N41-O41-P41-Q41)</f>
       </c>
       <c r="T41" s="3">
-        <f>IF($J41="","",(S41-V41)/I41*100)</f>
+        <f>IF($J41="","",(S41-Z41)/I41*100)</f>
       </c>
       <c r="U41" s="3">
         <f>IF($J41="","",L41-R41)</f>
       </c>
-      <c r="W41" s="3">
-        <f>IF($J41="","",S41-V41)</f>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA41" s="3">
+        <f>IF($J41="","",S41-Z41)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="I42" s="3"/>
@@ -2406,16 +2430,16 @@
         <f>IF($J42="","",K42-L42-M42-N42-O42-P42-Q42)</f>
       </c>
       <c r="T42" s="3">
-        <f>IF($J42="","",(S42-V42)/I42*100)</f>
+        <f>IF($J42="","",(S42-Z42)/I42*100)</f>
       </c>
       <c r="U42" s="3">
         <f>IF($J42="","",L42-R42)</f>
       </c>
-      <c r="W42" s="3">
-        <f>IF($J42="","",S42-V42)</f>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA42" s="3">
+        <f>IF($J42="","",S42-Z42)</f>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="I43" s="3"/>
@@ -2446,16 +2470,16 @@
         <f>IF($J43="","",K43-L43-M43-N43-O43-P43-Q43)</f>
       </c>
       <c r="T43" s="3">
-        <f>IF($J43="","",(S43-V43)/I43*100)</f>
+        <f>IF($J43="","",(S43-Z43)/I43*100)</f>
       </c>
       <c r="U43" s="3">
         <f>IF($J43="","",L43-R43)</f>
       </c>
-      <c r="W43" s="3">
-        <f>IF($J43="","",S43-V43)</f>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA43" s="3">
+        <f>IF($J43="","",S43-Z43)</f>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="I44" s="3"/>
@@ -2486,16 +2510,16 @@
         <f>IF($J44="","",K44-L44-M44-N44-O44-P44-Q44)</f>
       </c>
       <c r="T44" s="3">
-        <f>IF($J44="","",(S44-V44)/I44*100)</f>
+        <f>IF($J44="","",(S44-Z44)/I44*100)</f>
       </c>
       <c r="U44" s="3">
         <f>IF($J44="","",L44-R44)</f>
       </c>
-      <c r="W44" s="3">
-        <f>IF($J44="","",S44-V44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA44" s="3">
+        <f>IF($J44="","",S44-Z44)</f>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="I45" s="3"/>
@@ -2526,16 +2550,16 @@
         <f>IF($J45="","",K45-L45-M45-N45-O45-P45-Q45)</f>
       </c>
       <c r="T45" s="3">
-        <f>IF($J45="","",(S45-V45)/I45*100)</f>
+        <f>IF($J45="","",(S45-Z45)/I45*100)</f>
       </c>
       <c r="U45" s="3">
         <f>IF($J45="","",L45-R45)</f>
       </c>
-      <c r="W45" s="3">
-        <f>IF($J45="","",S45-V45)</f>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA45" s="3">
+        <f>IF($J45="","",S45-Z45)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="I46" s="3"/>
@@ -2566,16 +2590,16 @@
         <f>IF($J46="","",K46-L46-M46-N46-O46-P46-Q46)</f>
       </c>
       <c r="T46" s="3">
-        <f>IF($J46="","",(S46-V46)/I46*100)</f>
+        <f>IF($J46="","",(S46-Z46)/I46*100)</f>
       </c>
       <c r="U46" s="3">
         <f>IF($J46="","",L46-R46)</f>
       </c>
-      <c r="W46" s="3">
-        <f>IF($J46="","",S46-V46)</f>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA46" s="3">
+        <f>IF($J46="","",S46-Z46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="I47" s="3"/>
@@ -2606,16 +2630,16 @@
         <f>IF($J47="","",K47-L47-M47-N47-O47-P47-Q47)</f>
       </c>
       <c r="T47" s="3">
-        <f>IF($J47="","",(S47-V47)/I47*100)</f>
+        <f>IF($J47="","",(S47-Z47)/I47*100)</f>
       </c>
       <c r="U47" s="3">
         <f>IF($J47="","",L47-R47)</f>
       </c>
-      <c r="W47" s="3">
-        <f>IF($J47="","",S47-V47)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA47" s="3">
+        <f>IF($J47="","",S47-Z47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="I48" s="3"/>
@@ -2646,16 +2670,16 @@
         <f>IF($J48="","",K48-L48-M48-N48-O48-P48-Q48)</f>
       </c>
       <c r="T48" s="3">
-        <f>IF($J48="","",(S48-V48)/I48*100)</f>
+        <f>IF($J48="","",(S48-Z48)/I48*100)</f>
       </c>
       <c r="U48" s="3">
         <f>IF($J48="","",L48-R48)</f>
       </c>
-      <c r="W48" s="3">
-        <f>IF($J48="","",S48-V48)</f>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA48" s="3">
+        <f>IF($J48="","",S48-Z48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="I49" s="3"/>
@@ -2686,16 +2710,16 @@
         <f>IF($J49="","",K49-L49-M49-N49-O49-P49-Q49)</f>
       </c>
       <c r="T49" s="3">
-        <f>IF($J49="","",(S49-V49)/I49*100)</f>
+        <f>IF($J49="","",(S49-Z49)/I49*100)</f>
       </c>
       <c r="U49" s="3">
         <f>IF($J49="","",L49-R49)</f>
       </c>
-      <c r="W49" s="3">
-        <f>IF($J49="","",S49-V49)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA49" s="3">
+        <f>IF($J49="","",S49-Z49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="I50" s="3"/>
@@ -2726,16 +2750,16 @@
         <f>IF($J50="","",K50-L50-M50-N50-O50-P50-Q50)</f>
       </c>
       <c r="T50" s="3">
-        <f>IF($J50="","",(S50-V50)/I50*100)</f>
+        <f>IF($J50="","",(S50-Z50)/I50*100)</f>
       </c>
       <c r="U50" s="3">
         <f>IF($J50="","",L50-R50)</f>
       </c>
-      <c r="W50" s="3">
-        <f>IF($J50="","",S50-V50)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA50" s="3">
+        <f>IF($J50="","",S50-Z50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="I51" s="3"/>
@@ -2766,16 +2790,16 @@
         <f>IF($J51="","",K51-L51-M51-N51-O51-P51-Q51)</f>
       </c>
       <c r="T51" s="3">
-        <f>IF($J51="","",(S51-V51)/I51*100)</f>
+        <f>IF($J51="","",(S51-Z51)/I51*100)</f>
       </c>
       <c r="U51" s="3">
         <f>IF($J51="","",L51-R51)</f>
       </c>
-      <c r="W51" s="3">
-        <f>IF($J51="","",S51-V51)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA51" s="3">
+        <f>IF($J51="","",S51-Z51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="I52" s="3"/>
@@ -2806,16 +2830,16 @@
         <f>IF($J52="","",K52-L52-M52-N52-O52-P52-Q52)</f>
       </c>
       <c r="T52" s="3">
-        <f>IF($J52="","",(S52-V52)/I52*100)</f>
+        <f>IF($J52="","",(S52-Z52)/I52*100)</f>
       </c>
       <c r="U52" s="3">
         <f>IF($J52="","",L52-R52)</f>
       </c>
-      <c r="W52" s="3">
-        <f>IF($J52="","",S52-V52)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA52" s="3">
+        <f>IF($J52="","",S52-Z52)</f>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="I53" s="3"/>
@@ -2846,16 +2870,16 @@
         <f>IF($J53="","",K53-L53-M53-N53-O53-P53-Q53)</f>
       </c>
       <c r="T53" s="3">
-        <f>IF($J53="","",(S53-V53)/I53*100)</f>
+        <f>IF($J53="","",(S53-Z53)/I53*100)</f>
       </c>
       <c r="U53" s="3">
         <f>IF($J53="","",L53-R53)</f>
       </c>
-      <c r="W53" s="3">
-        <f>IF($J53="","",S53-V53)</f>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA53" s="3">
+        <f>IF($J53="","",S53-Z53)</f>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="I54" s="3"/>
@@ -2886,16 +2910,16 @@
         <f>IF($J54="","",K54-L54-M54-N54-O54-P54-Q54)</f>
       </c>
       <c r="T54" s="3">
-        <f>IF($J54="","",(S54-V54)/I54*100)</f>
+        <f>IF($J54="","",(S54-Z54)/I54*100)</f>
       </c>
       <c r="U54" s="3">
         <f>IF($J54="","",L54-R54)</f>
       </c>
-      <c r="W54" s="3">
-        <f>IF($J54="","",S54-V54)</f>
-      </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA54" s="3">
+        <f>IF($J54="","",S54-Z54)</f>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="I55" s="3"/>
@@ -2926,16 +2950,16 @@
         <f>IF($J55="","",K55-L55-M55-N55-O55-P55-Q55)</f>
       </c>
       <c r="T55" s="3">
-        <f>IF($J55="","",(S55-V55)/I55*100)</f>
+        <f>IF($J55="","",(S55-Z55)/I55*100)</f>
       </c>
       <c r="U55" s="3">
         <f>IF($J55="","",L55-R55)</f>
       </c>
-      <c r="W55" s="3">
-        <f>IF($J55="","",S55-V55)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA55" s="3">
+        <f>IF($J55="","",S55-Z55)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="I56" s="3"/>
@@ -2966,16 +2990,16 @@
         <f>IF($J56="","",K56-L56-M56-N56-O56-P56-Q56)</f>
       </c>
       <c r="T56" s="3">
-        <f>IF($J56="","",(S56-V56)/I56*100)</f>
+        <f>IF($J56="","",(S56-Z56)/I56*100)</f>
       </c>
       <c r="U56" s="3">
         <f>IF($J56="","",L56-R56)</f>
       </c>
-      <c r="W56" s="3">
-        <f>IF($J56="","",S56-V56)</f>
-      </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA56" s="3">
+        <f>IF($J56="","",S56-Z56)</f>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="I57" s="3"/>
@@ -3006,16 +3030,16 @@
         <f>IF($J57="","",K57-L57-M57-N57-O57-P57-Q57)</f>
       </c>
       <c r="T57" s="3">
-        <f>IF($J57="","",(S57-V57)/I57*100)</f>
+        <f>IF($J57="","",(S57-Z57)/I57*100)</f>
       </c>
       <c r="U57" s="3">
         <f>IF($J57="","",L57-R57)</f>
       </c>
-      <c r="W57" s="3">
-        <f>IF($J57="","",S57-V57)</f>
-      </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA57" s="3">
+        <f>IF($J57="","",S57-Z57)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="I58" s="3"/>
@@ -3046,16 +3070,16 @@
         <f>IF($J58="","",K58-L58-M58-N58-O58-P58-Q58)</f>
       </c>
       <c r="T58" s="3">
-        <f>IF($J58="","",(S58-V58)/I58*100)</f>
+        <f>IF($J58="","",(S58-Z58)/I58*100)</f>
       </c>
       <c r="U58" s="3">
         <f>IF($J58="","",L58-R58)</f>
       </c>
-      <c r="W58" s="3">
-        <f>IF($J58="","",S58-V58)</f>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA58" s="3">
+        <f>IF($J58="","",S58-Z58)</f>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="I59" s="3"/>
@@ -3086,16 +3110,16 @@
         <f>IF($J59="","",K59-L59-M59-N59-O59-P59-Q59)</f>
       </c>
       <c r="T59" s="3">
-        <f>IF($J59="","",(S59-V59)/I59*100)</f>
+        <f>IF($J59="","",(S59-Z59)/I59*100)</f>
       </c>
       <c r="U59" s="3">
         <f>IF($J59="","",L59-R59)</f>
       </c>
-      <c r="W59" s="3">
-        <f>IF($J59="","",S59-V59)</f>
-      </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA59" s="3">
+        <f>IF($J59="","",S59-Z59)</f>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="I60" s="3"/>
@@ -3126,16 +3150,16 @@
         <f>IF($J60="","",K60-L60-M60-N60-O60-P60-Q60)</f>
       </c>
       <c r="T60" s="3">
-        <f>IF($J60="","",(S60-V60)/I60*100)</f>
+        <f>IF($J60="","",(S60-Z60)/I60*100)</f>
       </c>
       <c r="U60" s="3">
         <f>IF($J60="","",L60-R60)</f>
       </c>
-      <c r="W60" s="3">
-        <f>IF($J60="","",S60-V60)</f>
-      </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA60" s="3">
+        <f>IF($J60="","",S60-Z60)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="I61" s="3"/>
@@ -3166,16 +3190,16 @@
         <f>IF($J61="","",K61-L61-M61-N61-O61-P61-Q61)</f>
       </c>
       <c r="T61" s="3">
-        <f>IF($J61="","",(S61-V61)/I61*100)</f>
+        <f>IF($J61="","",(S61-Z61)/I61*100)</f>
       </c>
       <c r="U61" s="3">
         <f>IF($J61="","",L61-R61)</f>
       </c>
-      <c r="W61" s="3">
-        <f>IF($J61="","",S61-V61)</f>
-      </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA61" s="3">
+        <f>IF($J61="","",S61-Z61)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="I62" s="3"/>
@@ -3206,16 +3230,16 @@
         <f>IF($J62="","",K62-L62-M62-N62-O62-P62-Q62)</f>
       </c>
       <c r="T62" s="3">
-        <f>IF($J62="","",(S62-V62)/I62*100)</f>
+        <f>IF($J62="","",(S62-Z62)/I62*100)</f>
       </c>
       <c r="U62" s="3">
         <f>IF($J62="","",L62-R62)</f>
       </c>
-      <c r="W62" s="3">
-        <f>IF($J62="","",S62-V62)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA62" s="3">
+        <f>IF($J62="","",S62-Z62)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="I63" s="3"/>
@@ -3246,16 +3270,16 @@
         <f>IF($J63="","",K63-L63-M63-N63-O63-P63-Q63)</f>
       </c>
       <c r="T63" s="3">
-        <f>IF($J63="","",(S63-V63)/I63*100)</f>
+        <f>IF($J63="","",(S63-Z63)/I63*100)</f>
       </c>
       <c r="U63" s="3">
         <f>IF($J63="","",L63-R63)</f>
       </c>
-      <c r="W63" s="3">
-        <f>IF($J63="","",S63-V63)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA63" s="3">
+        <f>IF($J63="","",S63-Z63)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="I64" s="3"/>
@@ -3286,16 +3310,16 @@
         <f>IF($J64="","",K64-L64-M64-N64-O64-P64-Q64)</f>
       </c>
       <c r="T64" s="3">
-        <f>IF($J64="","",(S64-V64)/I64*100)</f>
+        <f>IF($J64="","",(S64-Z64)/I64*100)</f>
       </c>
       <c r="U64" s="3">
         <f>IF($J64="","",L64-R64)</f>
       </c>
-      <c r="W64" s="3">
-        <f>IF($J64="","",S64-V64)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA64" s="3">
+        <f>IF($J64="","",S64-Z64)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="I65" s="3"/>
@@ -3326,16 +3350,16 @@
         <f>IF($J65="","",K65-L65-M65-N65-O65-P65-Q65)</f>
       </c>
       <c r="T65" s="3">
-        <f>IF($J65="","",(S65-V65)/I65*100)</f>
+        <f>IF($J65="","",(S65-Z65)/I65*100)</f>
       </c>
       <c r="U65" s="3">
         <f>IF($J65="","",L65-R65)</f>
       </c>
-      <c r="W65" s="3">
-        <f>IF($J65="","",S65-V65)</f>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA65" s="3">
+        <f>IF($J65="","",S65-Z65)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="I66" s="3"/>
@@ -3366,16 +3390,16 @@
         <f>IF($J66="","",K66-L66-M66-N66-O66-P66-Q66)</f>
       </c>
       <c r="T66" s="3">
-        <f>IF($J66="","",(S66-V66)/I66*100)</f>
+        <f>IF($J66="","",(S66-Z66)/I66*100)</f>
       </c>
       <c r="U66" s="3">
         <f>IF($J66="","",L66-R66)</f>
       </c>
-      <c r="W66" s="3">
-        <f>IF($J66="","",S66-V66)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA66" s="3">
+        <f>IF($J66="","",S66-Z66)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="I67" s="3"/>
@@ -3406,16 +3430,16 @@
         <f>IF($J67="","",K67-L67-M67-N67-O67-P67-Q67)</f>
       </c>
       <c r="T67" s="3">
-        <f>IF($J67="","",(S67-V67)/I67*100)</f>
+        <f>IF($J67="","",(S67-Z67)/I67*100)</f>
       </c>
       <c r="U67" s="3">
         <f>IF($J67="","",L67-R67)</f>
       </c>
-      <c r="W67" s="3">
-        <f>IF($J67="","",S67-V67)</f>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA67" s="3">
+        <f>IF($J67="","",S67-Z67)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="I68" s="3"/>
@@ -3446,16 +3470,16 @@
         <f>IF($J68="","",K68-L68-M68-N68-O68-P68-Q68)</f>
       </c>
       <c r="T68" s="3">
-        <f>IF($J68="","",(S68-V68)/I68*100)</f>
+        <f>IF($J68="","",(S68-Z68)/I68*100)</f>
       </c>
       <c r="U68" s="3">
         <f>IF($J68="","",L68-R68)</f>
       </c>
-      <c r="W68" s="3">
-        <f>IF($J68="","",S68-V68)</f>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA68" s="3">
+        <f>IF($J68="","",S68-Z68)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="I69" s="3"/>
@@ -3486,16 +3510,16 @@
         <f>IF($J69="","",K69-L69-M69-N69-O69-P69-Q69)</f>
       </c>
       <c r="T69" s="3">
-        <f>IF($J69="","",(S69-V69)/I69*100)</f>
+        <f>IF($J69="","",(S69-Z69)/I69*100)</f>
       </c>
       <c r="U69" s="3">
         <f>IF($J69="","",L69-R69)</f>
       </c>
-      <c r="W69" s="3">
-        <f>IF($J69="","",S69-V69)</f>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA69" s="3">
+        <f>IF($J69="","",S69-Z69)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="I70" s="3"/>
@@ -3526,16 +3550,16 @@
         <f>IF($J70="","",K70-L70-M70-N70-O70-P70-Q70)</f>
       </c>
       <c r="T70" s="3">
-        <f>IF($J70="","",(S70-V70)/I70*100)</f>
+        <f>IF($J70="","",(S70-Z70)/I70*100)</f>
       </c>
       <c r="U70" s="3">
         <f>IF($J70="","",L70-R70)</f>
       </c>
-      <c r="W70" s="3">
-        <f>IF($J70="","",S70-V70)</f>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA70" s="3">
+        <f>IF($J70="","",S70-Z70)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="I71" s="3"/>
@@ -3566,16 +3590,16 @@
         <f>IF($J71="","",K71-L71-M71-N71-O71-P71-Q71)</f>
       </c>
       <c r="T71" s="3">
-        <f>IF($J71="","",(S71-V71)/I71*100)</f>
+        <f>IF($J71="","",(S71-Z71)/I71*100)</f>
       </c>
       <c r="U71" s="3">
         <f>IF($J71="","",L71-R71)</f>
       </c>
-      <c r="W71" s="3">
-        <f>IF($J71="","",S71-V71)</f>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA71" s="3">
+        <f>IF($J71="","",S71-Z71)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="I72" s="3"/>
@@ -3606,16 +3630,16 @@
         <f>IF($J72="","",K72-L72-M72-N72-O72-P72-Q72)</f>
       </c>
       <c r="T72" s="3">
-        <f>IF($J72="","",(S72-V72)/I72*100)</f>
+        <f>IF($J72="","",(S72-Z72)/I72*100)</f>
       </c>
       <c r="U72" s="3">
         <f>IF($J72="","",L72-R72)</f>
       </c>
-      <c r="W72" s="3">
-        <f>IF($J72="","",S72-V72)</f>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA72" s="3">
+        <f>IF($J72="","",S72-Z72)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="I73" s="3"/>
@@ -3646,16 +3670,16 @@
         <f>IF($J73="","",K73-L73-M73-N73-O73-P73-Q73)</f>
       </c>
       <c r="T73" s="3">
-        <f>IF($J73="","",(S73-V73)/I73*100)</f>
+        <f>IF($J73="","",(S73-Z73)/I73*100)</f>
       </c>
       <c r="U73" s="3">
         <f>IF($J73="","",L73-R73)</f>
       </c>
-      <c r="W73" s="3">
-        <f>IF($J73="","",S73-V73)</f>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA73" s="3">
+        <f>IF($J73="","",S73-Z73)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="I74" s="3"/>
@@ -3686,16 +3710,16 @@
         <f>IF($J74="","",K74-L74-M74-N74-O74-P74-Q74)</f>
       </c>
       <c r="T74" s="3">
-        <f>IF($J74="","",(S74-V74)/I74*100)</f>
+        <f>IF($J74="","",(S74-Z74)/I74*100)</f>
       </c>
       <c r="U74" s="3">
         <f>IF($J74="","",L74-R74)</f>
       </c>
-      <c r="W74" s="3">
-        <f>IF($J74="","",S74-V74)</f>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA74" s="3">
+        <f>IF($J74="","",S74-Z74)</f>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="I75" s="3"/>
@@ -3726,16 +3750,16 @@
         <f>IF($J75="","",K75-L75-M75-N75-O75-P75-Q75)</f>
       </c>
       <c r="T75" s="3">
-        <f>IF($J75="","",(S75-V75)/I75*100)</f>
+        <f>IF($J75="","",(S75-Z75)/I75*100)</f>
       </c>
       <c r="U75" s="3">
         <f>IF($J75="","",L75-R75)</f>
       </c>
-      <c r="W75" s="3">
-        <f>IF($J75="","",S75-V75)</f>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA75" s="3">
+        <f>IF($J75="","",S75-Z75)</f>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="I76" s="3"/>
@@ -3766,16 +3790,16 @@
         <f>IF($J76="","",K76-L76-M76-N76-O76-P76-Q76)</f>
       </c>
       <c r="T76" s="3">
-        <f>IF($J76="","",(S76-V76)/I76*100)</f>
+        <f>IF($J76="","",(S76-Z76)/I76*100)</f>
       </c>
       <c r="U76" s="3">
         <f>IF($J76="","",L76-R76)</f>
       </c>
-      <c r="W76" s="3">
-        <f>IF($J76="","",S76-V76)</f>
-      </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA76" s="3">
+        <f>IF($J76="","",S76-Z76)</f>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="I77" s="3"/>
@@ -3806,16 +3830,16 @@
         <f>IF($J77="","",K77-L77-M77-N77-O77-P77-Q77)</f>
       </c>
       <c r="T77" s="3">
-        <f>IF($J77="","",(S77-V77)/I77*100)</f>
+        <f>IF($J77="","",(S77-Z77)/I77*100)</f>
       </c>
       <c r="U77" s="3">
         <f>IF($J77="","",L77-R77)</f>
       </c>
-      <c r="W77" s="3">
-        <f>IF($J77="","",S77-V77)</f>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA77" s="3">
+        <f>IF($J77="","",S77-Z77)</f>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="I78" s="3"/>
@@ -3846,16 +3870,16 @@
         <f>IF($J78="","",K78-L78-M78-N78-O78-P78-Q78)</f>
       </c>
       <c r="T78" s="3">
-        <f>IF($J78="","",(S78-V78)/I78*100)</f>
+        <f>IF($J78="","",(S78-Z78)/I78*100)</f>
       </c>
       <c r="U78" s="3">
         <f>IF($J78="","",L78-R78)</f>
       </c>
-      <c r="W78" s="3">
-        <f>IF($J78="","",S78-V78)</f>
-      </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA78" s="3">
+        <f>IF($J78="","",S78-Z78)</f>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="I79" s="3"/>
@@ -3886,16 +3910,16 @@
         <f>IF($J79="","",K79-L79-M79-N79-O79-P79-Q79)</f>
       </c>
       <c r="T79" s="3">
-        <f>IF($J79="","",(S79-V79)/I79*100)</f>
+        <f>IF($J79="","",(S79-Z79)/I79*100)</f>
       </c>
       <c r="U79" s="3">
         <f>IF($J79="","",L79-R79)</f>
       </c>
-      <c r="W79" s="3">
-        <f>IF($J79="","",S79-V79)</f>
-      </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA79" s="3">
+        <f>IF($J79="","",S79-Z79)</f>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="I80" s="3"/>
@@ -3926,16 +3950,16 @@
         <f>IF($J80="","",K80-L80-M80-N80-O80-P80-Q80)</f>
       </c>
       <c r="T80" s="3">
-        <f>IF($J80="","",(S80-V80)/I80*100)</f>
+        <f>IF($J80="","",(S80-Z80)/I80*100)</f>
       </c>
       <c r="U80" s="3">
         <f>IF($J80="","",L80-R80)</f>
       </c>
-      <c r="W80" s="3">
-        <f>IF($J80="","",S80-V80)</f>
-      </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA80" s="3">
+        <f>IF($J80="","",S80-Z80)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="I81" s="3"/>
@@ -3966,16 +3990,16 @@
         <f>IF($J81="","",K81-L81-M81-N81-O81-P81-Q81)</f>
       </c>
       <c r="T81" s="3">
-        <f>IF($J81="","",(S81-V81)/I81*100)</f>
+        <f>IF($J81="","",(S81-Z81)/I81*100)</f>
       </c>
       <c r="U81" s="3">
         <f>IF($J81="","",L81-R81)</f>
       </c>
-      <c r="W81" s="3">
-        <f>IF($J81="","",S81-V81)</f>
-      </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA81" s="3">
+        <f>IF($J81="","",S81-Z81)</f>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="I82" s="3"/>
@@ -4006,16 +4030,16 @@
         <f>IF($J82="","",K82-L82-M82-N82-O82-P82-Q82)</f>
       </c>
       <c r="T82" s="3">
-        <f>IF($J82="","",(S82-V82)/I82*100)</f>
+        <f>IF($J82="","",(S82-Z82)/I82*100)</f>
       </c>
       <c r="U82" s="3">
         <f>IF($J82="","",L82-R82)</f>
       </c>
-      <c r="W82" s="3">
-        <f>IF($J82="","",S82-V82)</f>
-      </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA82" s="3">
+        <f>IF($J82="","",S82-Z82)</f>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="I83" s="3"/>
@@ -4046,16 +4070,16 @@
         <f>IF($J83="","",K83-L83-M83-N83-O83-P83-Q83)</f>
       </c>
       <c r="T83" s="3">
-        <f>IF($J83="","",(S83-V83)/I83*100)</f>
+        <f>IF($J83="","",(S83-Z83)/I83*100)</f>
       </c>
       <c r="U83" s="3">
         <f>IF($J83="","",L83-R83)</f>
       </c>
-      <c r="W83" s="3">
-        <f>IF($J83="","",S83-V83)</f>
-      </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA83" s="3">
+        <f>IF($J83="","",S83-Z83)</f>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="I84" s="3"/>
@@ -4086,16 +4110,16 @@
         <f>IF($J84="","",K84-L84-M84-N84-O84-P84-Q84)</f>
       </c>
       <c r="T84" s="3">
-        <f>IF($J84="","",(S84-V84)/I84*100)</f>
+        <f>IF($J84="","",(S84-Z84)/I84*100)</f>
       </c>
       <c r="U84" s="3">
         <f>IF($J84="","",L84-R84)</f>
       </c>
-      <c r="W84" s="3">
-        <f>IF($J84="","",S84-V84)</f>
-      </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA84" s="3">
+        <f>IF($J84="","",S84-Z84)</f>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="I85" s="3"/>
@@ -4126,16 +4150,16 @@
         <f>IF($J85="","",K85-L85-M85-N85-O85-P85-Q85)</f>
       </c>
       <c r="T85" s="3">
-        <f>IF($J85="","",(S85-V85)/I85*100)</f>
+        <f>IF($J85="","",(S85-Z85)/I85*100)</f>
       </c>
       <c r="U85" s="3">
         <f>IF($J85="","",L85-R85)</f>
       </c>
-      <c r="W85" s="3">
-        <f>IF($J85="","",S85-V85)</f>
-      </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA85" s="3">
+        <f>IF($J85="","",S85-Z85)</f>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="I86" s="3"/>
@@ -4166,16 +4190,16 @@
         <f>IF($J86="","",K86-L86-M86-N86-O86-P86-Q86)</f>
       </c>
       <c r="T86" s="3">
-        <f>IF($J86="","",(S86-V86)/I86*100)</f>
+        <f>IF($J86="","",(S86-Z86)/I86*100)</f>
       </c>
       <c r="U86" s="3">
         <f>IF($J86="","",L86-R86)</f>
       </c>
-      <c r="W86" s="3">
-        <f>IF($J86="","",S86-V86)</f>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA86" s="3">
+        <f>IF($J86="","",S86-Z86)</f>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="I87" s="3"/>
@@ -4206,16 +4230,16 @@
         <f>IF($J87="","",K87-L87-M87-N87-O87-P87-Q87)</f>
       </c>
       <c r="T87" s="3">
-        <f>IF($J87="","",(S87-V87)/I87*100)</f>
+        <f>IF($J87="","",(S87-Z87)/I87*100)</f>
       </c>
       <c r="U87" s="3">
         <f>IF($J87="","",L87-R87)</f>
       </c>
-      <c r="W87" s="3">
-        <f>IF($J87="","",S87-V87)</f>
-      </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA87" s="3">
+        <f>IF($J87="","",S87-Z87)</f>
+      </c>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="I88" s="3"/>
@@ -4246,16 +4270,16 @@
         <f>IF($J88="","",K88-L88-M88-N88-O88-P88-Q88)</f>
       </c>
       <c r="T88" s="3">
-        <f>IF($J88="","",(S88-V88)/I88*100)</f>
+        <f>IF($J88="","",(S88-Z88)/I88*100)</f>
       </c>
       <c r="U88" s="3">
         <f>IF($J88="","",L88-R88)</f>
       </c>
-      <c r="W88" s="3">
-        <f>IF($J88="","",S88-V88)</f>
-      </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA88" s="3">
+        <f>IF($J88="","",S88-Z88)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="I89" s="3"/>
@@ -4286,16 +4310,16 @@
         <f>IF($J89="","",K89-L89-M89-N89-O89-P89-Q89)</f>
       </c>
       <c r="T89" s="3">
-        <f>IF($J89="","",(S89-V89)/I89*100)</f>
+        <f>IF($J89="","",(S89-Z89)/I89*100)</f>
       </c>
       <c r="U89" s="3">
         <f>IF($J89="","",L89-R89)</f>
       </c>
-      <c r="W89" s="3">
-        <f>IF($J89="","",S89-V89)</f>
-      </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA89" s="3">
+        <f>IF($J89="","",S89-Z89)</f>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="I90" s="3"/>
@@ -4326,16 +4350,16 @@
         <f>IF($J90="","",K90-L90-M90-N90-O90-P90-Q90)</f>
       </c>
       <c r="T90" s="3">
-        <f>IF($J90="","",(S90-V90)/I90*100)</f>
+        <f>IF($J90="","",(S90-Z90)/I90*100)</f>
       </c>
       <c r="U90" s="3">
         <f>IF($J90="","",L90-R90)</f>
       </c>
-      <c r="W90" s="3">
-        <f>IF($J90="","",S90-V90)</f>
-      </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA90" s="3">
+        <f>IF($J90="","",S90-Z90)</f>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="I91" s="3"/>
@@ -4366,16 +4390,16 @@
         <f>IF($J91="","",K91-L91-M91-N91-O91-P91-Q91)</f>
       </c>
       <c r="T91" s="3">
-        <f>IF($J91="","",(S91-V91)/I91*100)</f>
+        <f>IF($J91="","",(S91-Z91)/I91*100)</f>
       </c>
       <c r="U91" s="3">
         <f>IF($J91="","",L91-R91)</f>
       </c>
-      <c r="W91" s="3">
-        <f>IF($J91="","",S91-V91)</f>
-      </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA91" s="3">
+        <f>IF($J91="","",S91-Z91)</f>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="I92" s="3"/>
@@ -4406,16 +4430,16 @@
         <f>IF($J92="","",K92-L92-M92-N92-O92-P92-Q92)</f>
       </c>
       <c r="T92" s="3">
-        <f>IF($J92="","",(S92-V92)/I92*100)</f>
+        <f>IF($J92="","",(S92-Z92)/I92*100)</f>
       </c>
       <c r="U92" s="3">
         <f>IF($J92="","",L92-R92)</f>
       </c>
-      <c r="W92" s="3">
-        <f>IF($J92="","",S92-V92)</f>
-      </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA92" s="3">
+        <f>IF($J92="","",S92-Z92)</f>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="I93" s="3"/>
@@ -4446,16 +4470,16 @@
         <f>IF($J93="","",K93-L93-M93-N93-O93-P93-Q93)</f>
       </c>
       <c r="T93" s="3">
-        <f>IF($J93="","",(S93-V93)/I93*100)</f>
+        <f>IF($J93="","",(S93-Z93)/I93*100)</f>
       </c>
       <c r="U93" s="3">
         <f>IF($J93="","",L93-R93)</f>
       </c>
-      <c r="W93" s="3">
-        <f>IF($J93="","",S93-V93)</f>
-      </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA93" s="3">
+        <f>IF($J93="","",S93-Z93)</f>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="I94" s="3"/>
@@ -4486,16 +4510,16 @@
         <f>IF($J94="","",K94-L94-M94-N94-O94-P94-Q94)</f>
       </c>
       <c r="T94" s="3">
-        <f>IF($J94="","",(S94-V94)/I94*100)</f>
+        <f>IF($J94="","",(S94-Z94)/I94*100)</f>
       </c>
       <c r="U94" s="3">
         <f>IF($J94="","",L94-R94)</f>
       </c>
-      <c r="W94" s="3">
-        <f>IF($J94="","",S94-V94)</f>
-      </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA94" s="3">
+        <f>IF($J94="","",S94-Z94)</f>
+      </c>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="I95" s="3"/>
@@ -4526,16 +4550,16 @@
         <f>IF($J95="","",K95-L95-M95-N95-O95-P95-Q95)</f>
       </c>
       <c r="T95" s="3">
-        <f>IF($J95="","",(S95-V95)/I95*100)</f>
+        <f>IF($J95="","",(S95-Z95)/I95*100)</f>
       </c>
       <c r="U95" s="3">
         <f>IF($J95="","",L95-R95)</f>
       </c>
-      <c r="W95" s="3">
-        <f>IF($J95="","",S95-V95)</f>
-      </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA95" s="3">
+        <f>IF($J95="","",S95-Z95)</f>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="I96" s="3"/>
@@ -4566,16 +4590,16 @@
         <f>IF($J96="","",K96-L96-M96-N96-O96-P96-Q96)</f>
       </c>
       <c r="T96" s="3">
-        <f>IF($J96="","",(S96-V96)/I96*100)</f>
+        <f>IF($J96="","",(S96-Z96)/I96*100)</f>
       </c>
       <c r="U96" s="3">
         <f>IF($J96="","",L96-R96)</f>
       </c>
-      <c r="W96" s="3">
-        <f>IF($J96="","",S96-V96)</f>
-      </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA96" s="3">
+        <f>IF($J96="","",S96-Z96)</f>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="I97" s="3"/>
@@ -4606,16 +4630,16 @@
         <f>IF($J97="","",K97-L97-M97-N97-O97-P97-Q97)</f>
       </c>
       <c r="T97" s="3">
-        <f>IF($J97="","",(S97-V97)/I97*100)</f>
+        <f>IF($J97="","",(S97-Z97)/I97*100)</f>
       </c>
       <c r="U97" s="3">
         <f>IF($J97="","",L97-R97)</f>
       </c>
-      <c r="W97" s="3">
-        <f>IF($J97="","",S97-V97)</f>
-      </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA97" s="3">
+        <f>IF($J97="","",S97-Z97)</f>
+      </c>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="I98" s="3"/>
@@ -4646,16 +4670,16 @@
         <f>IF($J98="","",K98-L98-M98-N98-O98-P98-Q98)</f>
       </c>
       <c r="T98" s="3">
-        <f>IF($J98="","",(S98-V98)/I98*100)</f>
+        <f>IF($J98="","",(S98-Z98)/I98*100)</f>
       </c>
       <c r="U98" s="3">
         <f>IF($J98="","",L98-R98)</f>
       </c>
-      <c r="W98" s="3">
-        <f>IF($J98="","",S98-V98)</f>
-      </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA98" s="3">
+        <f>IF($J98="","",S98-Z98)</f>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="I99" s="3"/>
@@ -4686,16 +4710,16 @@
         <f>IF($J99="","",K99-L99-M99-N99-O99-P99-Q99)</f>
       </c>
       <c r="T99" s="3">
-        <f>IF($J99="","",(S99-V99)/I99*100)</f>
+        <f>IF($J99="","",(S99-Z99)/I99*100)</f>
       </c>
       <c r="U99" s="3">
         <f>IF($J99="","",L99-R99)</f>
       </c>
-      <c r="W99" s="3">
-        <f>IF($J99="","",S99-V99)</f>
-      </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA99" s="3">
+        <f>IF($J99="","",S99-Z99)</f>
+      </c>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="I100" s="3"/>
@@ -4726,16 +4750,16 @@
         <f>IF($J100="","",K100-L100-M100-N100-O100-P100-Q100)</f>
       </c>
       <c r="T100" s="3">
-        <f>IF($J100="","",(S100-V100)/I100*100)</f>
+        <f>IF($J100="","",(S100-Z100)/I100*100)</f>
       </c>
       <c r="U100" s="3">
         <f>IF($J100="","",L100-R100)</f>
       </c>
-      <c r="W100" s="3">
-        <f>IF($J100="","",S100-V100)</f>
-      </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA100" s="3">
+        <f>IF($J100="","",S100-Z100)</f>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="I101" s="3"/>
@@ -4766,16 +4790,16 @@
         <f>IF($J101="","",K101-L101-M101-N101-O101-P101-Q101)</f>
       </c>
       <c r="T101" s="3">
-        <f>IF($J101="","",(S101-V101)/I101*100)</f>
+        <f>IF($J101="","",(S101-Z101)/I101*100)</f>
       </c>
       <c r="U101" s="3">
         <f>IF($J101="","",L101-R101)</f>
       </c>
-      <c r="W101" s="3">
-        <f>IF($J101="","",S101-V101)</f>
-      </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA101" s="3">
+        <f>IF($J101="","",S101-Z101)</f>
+      </c>
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="I102" s="3"/>
@@ -4806,16 +4830,16 @@
         <f>IF($J102="","",K102-L102-M102-N102-O102-P102-Q102)</f>
       </c>
       <c r="T102" s="3">
-        <f>IF($J102="","",(S102-V102)/I102*100)</f>
+        <f>IF($J102="","",(S102-Z102)/I102*100)</f>
       </c>
       <c r="U102" s="3">
         <f>IF($J102="","",L102-R102)</f>
       </c>
-      <c r="W102" s="3">
-        <f>IF($J102="","",S102-V102)</f>
-      </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA102" s="3">
+        <f>IF($J102="","",S102-Z102)</f>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="I103" s="3"/>
@@ -4846,16 +4870,16 @@
         <f>IF($J103="","",K103-L103-M103-N103-O103-P103-Q103)</f>
       </c>
       <c r="T103" s="3">
-        <f>IF($J103="","",(S103-V103)/I103*100)</f>
+        <f>IF($J103="","",(S103-Z103)/I103*100)</f>
       </c>
       <c r="U103" s="3">
         <f>IF($J103="","",L103-R103)</f>
       </c>
-      <c r="W103" s="3">
-        <f>IF($J103="","",S103-V103)</f>
-      </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA103" s="3">
+        <f>IF($J103="","",S103-Z103)</f>
+      </c>
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="I104" s="3"/>
@@ -4886,16 +4910,16 @@
         <f>IF($J104="","",K104-L104-M104-N104-O104-P104-Q104)</f>
       </c>
       <c r="T104" s="3">
-        <f>IF($J104="","",(S104-V104)/I104*100)</f>
+        <f>IF($J104="","",(S104-Z104)/I104*100)</f>
       </c>
       <c r="U104" s="3">
         <f>IF($J104="","",L104-R104)</f>
       </c>
-      <c r="W104" s="3">
-        <f>IF($J104="","",S104-V104)</f>
-      </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA104" s="3">
+        <f>IF($J104="","",S104-Z104)</f>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="I105" s="3"/>
@@ -4926,16 +4950,16 @@
         <f>IF($J105="","",K105-L105-M105-N105-O105-P105-Q105)</f>
       </c>
       <c r="T105" s="3">
-        <f>IF($J105="","",(S105-V105)/I105*100)</f>
+        <f>IF($J105="","",(S105-Z105)/I105*100)</f>
       </c>
       <c r="U105" s="3">
         <f>IF($J105="","",L105-R105)</f>
       </c>
-      <c r="W105" s="3">
-        <f>IF($J105="","",S105-V105)</f>
-      </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA105" s="3">
+        <f>IF($J105="","",S105-Z105)</f>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="I106" s="3"/>
@@ -4966,16 +4990,16 @@
         <f>IF($J106="","",K106-L106-M106-N106-O106-P106-Q106)</f>
       </c>
       <c r="T106" s="3">
-        <f>IF($J106="","",(S106-V106)/I106*100)</f>
+        <f>IF($J106="","",(S106-Z106)/I106*100)</f>
       </c>
       <c r="U106" s="3">
         <f>IF($J106="","",L106-R106)</f>
       </c>
-      <c r="W106" s="3">
-        <f>IF($J106="","",S106-V106)</f>
-      </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA106" s="3">
+        <f>IF($J106="","",S106-Z106)</f>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="I107" s="3"/>
@@ -5006,16 +5030,16 @@
         <f>IF($J107="","",K107-L107-M107-N107-O107-P107-Q107)</f>
       </c>
       <c r="T107" s="3">
-        <f>IF($J107="","",(S107-V107)/I107*100)</f>
+        <f>IF($J107="","",(S107-Z107)/I107*100)</f>
       </c>
       <c r="U107" s="3">
         <f>IF($J107="","",L107-R107)</f>
       </c>
-      <c r="W107" s="3">
-        <f>IF($J107="","",S107-V107)</f>
-      </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA107" s="3">
+        <f>IF($J107="","",S107-Z107)</f>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="I108" s="3"/>
@@ -5046,16 +5070,16 @@
         <f>IF($J108="","",K108-L108-M108-N108-O108-P108-Q108)</f>
       </c>
       <c r="T108" s="3">
-        <f>IF($J108="","",(S108-V108)/I108*100)</f>
+        <f>IF($J108="","",(S108-Z108)/I108*100)</f>
       </c>
       <c r="U108" s="3">
         <f>IF($J108="","",L108-R108)</f>
       </c>
-      <c r="W108" s="3">
-        <f>IF($J108="","",S108-V108)</f>
-      </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA108" s="3">
+        <f>IF($J108="","",S108-Z108)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="I109" s="3"/>
@@ -5086,16 +5110,16 @@
         <f>IF($J109="","",K109-L109-M109-N109-O109-P109-Q109)</f>
       </c>
       <c r="T109" s="3">
-        <f>IF($J109="","",(S109-V109)/I109*100)</f>
+        <f>IF($J109="","",(S109-Z109)/I109*100)</f>
       </c>
       <c r="U109" s="3">
         <f>IF($J109="","",L109-R109)</f>
       </c>
-      <c r="W109" s="3">
-        <f>IF($J109="","",S109-V109)</f>
-      </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA109" s="3">
+        <f>IF($J109="","",S109-Z109)</f>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="I110" s="3"/>
@@ -5126,16 +5150,16 @@
         <f>IF($J110="","",K110-L110-M110-N110-O110-P110-Q110)</f>
       </c>
       <c r="T110" s="3">
-        <f>IF($J110="","",(S110-V110)/I110*100)</f>
+        <f>IF($J110="","",(S110-Z110)/I110*100)</f>
       </c>
       <c r="U110" s="3">
         <f>IF($J110="","",L110-R110)</f>
       </c>
-      <c r="W110" s="3">
-        <f>IF($J110="","",S110-V110)</f>
-      </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA110" s="3">
+        <f>IF($J110="","",S110-Z110)</f>
+      </c>
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="I111" s="3"/>
@@ -5166,16 +5190,16 @@
         <f>IF($J111="","",K111-L111-M111-N111-O111-P111-Q111)</f>
       </c>
       <c r="T111" s="3">
-        <f>IF($J111="","",(S111-V111)/I111*100)</f>
+        <f>IF($J111="","",(S111-Z111)/I111*100)</f>
       </c>
       <c r="U111" s="3">
         <f>IF($J111="","",L111-R111)</f>
       </c>
-      <c r="W111" s="3">
-        <f>IF($J111="","",S111-V111)</f>
-      </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA111" s="3">
+        <f>IF($J111="","",S111-Z111)</f>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="I112" s="3"/>
@@ -5206,16 +5230,16 @@
         <f>IF($J112="","",K112-L112-M112-N112-O112-P112-Q112)</f>
       </c>
       <c r="T112" s="3">
-        <f>IF($J112="","",(S112-V112)/I112*100)</f>
+        <f>IF($J112="","",(S112-Z112)/I112*100)</f>
       </c>
       <c r="U112" s="3">
         <f>IF($J112="","",L112-R112)</f>
       </c>
-      <c r="W112" s="3">
-        <f>IF($J112="","",S112-V112)</f>
-      </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA112" s="3">
+        <f>IF($J112="","",S112-Z112)</f>
+      </c>
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="I113" s="3"/>
@@ -5246,16 +5270,16 @@
         <f>IF($J113="","",K113-L113-M113-N113-O113-P113-Q113)</f>
       </c>
       <c r="T113" s="3">
-        <f>IF($J113="","",(S113-V113)/I113*100)</f>
+        <f>IF($J113="","",(S113-Z113)/I113*100)</f>
       </c>
       <c r="U113" s="3">
         <f>IF($J113="","",L113-R113)</f>
       </c>
-      <c r="W113" s="3">
-        <f>IF($J113="","",S113-V113)</f>
-      </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA113" s="3">
+        <f>IF($J113="","",S113-Z113)</f>
+      </c>
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="I114" s="3"/>
@@ -5286,16 +5310,16 @@
         <f>IF($J114="","",K114-L114-M114-N114-O114-P114-Q114)</f>
       </c>
       <c r="T114" s="3">
-        <f>IF($J114="","",(S114-V114)/I114*100)</f>
+        <f>IF($J114="","",(S114-Z114)/I114*100)</f>
       </c>
       <c r="U114" s="3">
         <f>IF($J114="","",L114-R114)</f>
       </c>
-      <c r="W114" s="3">
-        <f>IF($J114="","",S114-V114)</f>
-      </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA114" s="3">
+        <f>IF($J114="","",S114-Z114)</f>
+      </c>
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="I115" s="3"/>
@@ -5326,16 +5350,16 @@
         <f>IF($J115="","",K115-L115-M115-N115-O115-P115-Q115)</f>
       </c>
       <c r="T115" s="3">
-        <f>IF($J115="","",(S115-V115)/I115*100)</f>
+        <f>IF($J115="","",(S115-Z115)/I115*100)</f>
       </c>
       <c r="U115" s="3">
         <f>IF($J115="","",L115-R115)</f>
       </c>
-      <c r="W115" s="3">
-        <f>IF($J115="","",S115-V115)</f>
-      </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA115" s="3">
+        <f>IF($J115="","",S115-Z115)</f>
+      </c>
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="I116" s="3"/>
@@ -5366,16 +5390,16 @@
         <f>IF($J116="","",K116-L116-M116-N116-O116-P116-Q116)</f>
       </c>
       <c r="T116" s="3">
-        <f>IF($J116="","",(S116-V116)/I116*100)</f>
+        <f>IF($J116="","",(S116-Z116)/I116*100)</f>
       </c>
       <c r="U116" s="3">
         <f>IF($J116="","",L116-R116)</f>
       </c>
-      <c r="W116" s="3">
-        <f>IF($J116="","",S116-V116)</f>
-      </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA116" s="3">
+        <f>IF($J116="","",S116-Z116)</f>
+      </c>
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="I117" s="3"/>
@@ -5406,16 +5430,16 @@
         <f>IF($J117="","",K117-L117-M117-N117-O117-P117-Q117)</f>
       </c>
       <c r="T117" s="3">
-        <f>IF($J117="","",(S117-V117)/I117*100)</f>
+        <f>IF($J117="","",(S117-Z117)/I117*100)</f>
       </c>
       <c r="U117" s="3">
         <f>IF($J117="","",L117-R117)</f>
       </c>
-      <c r="W117" s="3">
-        <f>IF($J117="","",S117-V117)</f>
-      </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA117" s="3">
+        <f>IF($J117="","",S117-Z117)</f>
+      </c>
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="I118" s="3"/>
@@ -5446,16 +5470,16 @@
         <f>IF($J118="","",K118-L118-M118-N118-O118-P118-Q118)</f>
       </c>
       <c r="T118" s="3">
-        <f>IF($J118="","",(S118-V118)/I118*100)</f>
+        <f>IF($J118="","",(S118-Z118)/I118*100)</f>
       </c>
       <c r="U118" s="3">
         <f>IF($J118="","",L118-R118)</f>
       </c>
-      <c r="W118" s="3">
-        <f>IF($J118="","",S118-V118)</f>
-      </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA118" s="3">
+        <f>IF($J118="","",S118-Z118)</f>
+      </c>
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="I119" s="3"/>
@@ -5486,16 +5510,16 @@
         <f>IF($J119="","",K119-L119-M119-N119-O119-P119-Q119)</f>
       </c>
       <c r="T119" s="3">
-        <f>IF($J119="","",(S119-V119)/I119*100)</f>
+        <f>IF($J119="","",(S119-Z119)/I119*100)</f>
       </c>
       <c r="U119" s="3">
         <f>IF($J119="","",L119-R119)</f>
       </c>
-      <c r="W119" s="3">
-        <f>IF($J119="","",S119-V119)</f>
-      </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA119" s="3">
+        <f>IF($J119="","",S119-Z119)</f>
+      </c>
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="I120" s="3"/>
@@ -5526,16 +5550,16 @@
         <f>IF($J120="","",K120-L120-M120-N120-O120-P120-Q120)</f>
       </c>
       <c r="T120" s="3">
-        <f>IF($J120="","",(S120-V120)/I120*100)</f>
+        <f>IF($J120="","",(S120-Z120)/I120*100)</f>
       </c>
       <c r="U120" s="3">
         <f>IF($J120="","",L120-R120)</f>
       </c>
-      <c r="W120" s="3">
-        <f>IF($J120="","",S120-V120)</f>
-      </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA120" s="3">
+        <f>IF($J120="","",S120-Z120)</f>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="I121" s="3"/>
@@ -5566,16 +5590,16 @@
         <f>IF($J121="","",K121-L121-M121-N121-O121-P121-Q121)</f>
       </c>
       <c r="T121" s="3">
-        <f>IF($J121="","",(S121-V121)/I121*100)</f>
+        <f>IF($J121="","",(S121-Z121)/I121*100)</f>
       </c>
       <c r="U121" s="3">
         <f>IF($J121="","",L121-R121)</f>
       </c>
-      <c r="W121" s="3">
-        <f>IF($J121="","",S121-V121)</f>
-      </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA121" s="3">
+        <f>IF($J121="","",S121-Z121)</f>
+      </c>
+    </row>
+    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="I122" s="3"/>
@@ -5606,16 +5630,16 @@
         <f>IF($J122="","",K122-L122-M122-N122-O122-P122-Q122)</f>
       </c>
       <c r="T122" s="3">
-        <f>IF($J122="","",(S122-V122)/I122*100)</f>
+        <f>IF($J122="","",(S122-Z122)/I122*100)</f>
       </c>
       <c r="U122" s="3">
         <f>IF($J122="","",L122-R122)</f>
       </c>
-      <c r="W122" s="3">
-        <f>IF($J122="","",S122-V122)</f>
-      </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA122" s="3">
+        <f>IF($J122="","",S122-Z122)</f>
+      </c>
+    </row>
+    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="I123" s="3"/>
@@ -5646,16 +5670,16 @@
         <f>IF($J123="","",K123-L123-M123-N123-O123-P123-Q123)</f>
       </c>
       <c r="T123" s="3">
-        <f>IF($J123="","",(S123-V123)/I123*100)</f>
+        <f>IF($J123="","",(S123-Z123)/I123*100)</f>
       </c>
       <c r="U123" s="3">
         <f>IF($J123="","",L123-R123)</f>
       </c>
-      <c r="W123" s="3">
-        <f>IF($J123="","",S123-V123)</f>
-      </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA123" s="3">
+        <f>IF($J123="","",S123-Z123)</f>
+      </c>
+    </row>
+    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="I124" s="3"/>
@@ -5686,16 +5710,16 @@
         <f>IF($J124="","",K124-L124-M124-N124-O124-P124-Q124)</f>
       </c>
       <c r="T124" s="3">
-        <f>IF($J124="","",(S124-V124)/I124*100)</f>
+        <f>IF($J124="","",(S124-Z124)/I124*100)</f>
       </c>
       <c r="U124" s="3">
         <f>IF($J124="","",L124-R124)</f>
       </c>
-      <c r="W124" s="3">
-        <f>IF($J124="","",S124-V124)</f>
-      </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA124" s="3">
+        <f>IF($J124="","",S124-Z124)</f>
+      </c>
+    </row>
+    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="I125" s="3"/>
@@ -5726,16 +5750,16 @@
         <f>IF($J125="","",K125-L125-M125-N125-O125-P125-Q125)</f>
       </c>
       <c r="T125" s="3">
-        <f>IF($J125="","",(S125-V125)/I125*100)</f>
+        <f>IF($J125="","",(S125-Z125)/I125*100)</f>
       </c>
       <c r="U125" s="3">
         <f>IF($J125="","",L125-R125)</f>
       </c>
-      <c r="W125" s="3">
-        <f>IF($J125="","",S125-V125)</f>
-      </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA125" s="3">
+        <f>IF($J125="","",S125-Z125)</f>
+      </c>
+    </row>
+    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="I126" s="3"/>
@@ -5766,16 +5790,16 @@
         <f>IF($J126="","",K126-L126-M126-N126-O126-P126-Q126)</f>
       </c>
       <c r="T126" s="3">
-        <f>IF($J126="","",(S126-V126)/I126*100)</f>
+        <f>IF($J126="","",(S126-Z126)/I126*100)</f>
       </c>
       <c r="U126" s="3">
         <f>IF($J126="","",L126-R126)</f>
       </c>
-      <c r="W126" s="3">
-        <f>IF($J126="","",S126-V126)</f>
-      </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA126" s="3">
+        <f>IF($J126="","",S126-Z126)</f>
+      </c>
+    </row>
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="I127" s="3"/>
@@ -5806,16 +5830,16 @@
         <f>IF($J127="","",K127-L127-M127-N127-O127-P127-Q127)</f>
       </c>
       <c r="T127" s="3">
-        <f>IF($J127="","",(S127-V127)/I127*100)</f>
+        <f>IF($J127="","",(S127-Z127)/I127*100)</f>
       </c>
       <c r="U127" s="3">
         <f>IF($J127="","",L127-R127)</f>
       </c>
-      <c r="W127" s="3">
-        <f>IF($J127="","",S127-V127)</f>
-      </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA127" s="3">
+        <f>IF($J127="","",S127-Z127)</f>
+      </c>
+    </row>
+    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="I128" s="3"/>
@@ -5846,16 +5870,16 @@
         <f>IF($J128="","",K128-L128-M128-N128-O128-P128-Q128)</f>
       </c>
       <c r="T128" s="3">
-        <f>IF($J128="","",(S128-V128)/I128*100)</f>
+        <f>IF($J128="","",(S128-Z128)/I128*100)</f>
       </c>
       <c r="U128" s="3">
         <f>IF($J128="","",L128-R128)</f>
       </c>
-      <c r="W128" s="3">
-        <f>IF($J128="","",S128-V128)</f>
-      </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA128" s="3">
+        <f>IF($J128="","",S128-Z128)</f>
+      </c>
+    </row>
+    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="I129" s="3"/>
@@ -5886,16 +5910,16 @@
         <f>IF($J129="","",K129-L129-M129-N129-O129-P129-Q129)</f>
       </c>
       <c r="T129" s="3">
-        <f>IF($J129="","",(S129-V129)/I129*100)</f>
+        <f>IF($J129="","",(S129-Z129)/I129*100)</f>
       </c>
       <c r="U129" s="3">
         <f>IF($J129="","",L129-R129)</f>
       </c>
-      <c r="W129" s="3">
-        <f>IF($J129="","",S129-V129)</f>
-      </c>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA129" s="3">
+        <f>IF($J129="","",S129-Z129)</f>
+      </c>
+    </row>
+    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="I130" s="3"/>
@@ -5926,16 +5950,16 @@
         <f>IF($J130="","",K130-L130-M130-N130-O130-P130-Q130)</f>
       </c>
       <c r="T130" s="3">
-        <f>IF($J130="","",(S130-V130)/I130*100)</f>
+        <f>IF($J130="","",(S130-Z130)/I130*100)</f>
       </c>
       <c r="U130" s="3">
         <f>IF($J130="","",L130-R130)</f>
       </c>
-      <c r="W130" s="3">
-        <f>IF($J130="","",S130-V130)</f>
-      </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA130" s="3">
+        <f>IF($J130="","",S130-Z130)</f>
+      </c>
+    </row>
+    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="I131" s="3"/>
@@ -5966,16 +5990,16 @@
         <f>IF($J131="","",K131-L131-M131-N131-O131-P131-Q131)</f>
       </c>
       <c r="T131" s="3">
-        <f>IF($J131="","",(S131-V131)/I131*100)</f>
+        <f>IF($J131="","",(S131-Z131)/I131*100)</f>
       </c>
       <c r="U131" s="3">
         <f>IF($J131="","",L131-R131)</f>
       </c>
-      <c r="W131" s="3">
-        <f>IF($J131="","",S131-V131)</f>
-      </c>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA131" s="3">
+        <f>IF($J131="","",S131-Z131)</f>
+      </c>
+    </row>
+    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="I132" s="3"/>
@@ -6006,16 +6030,16 @@
         <f>IF($J132="","",K132-L132-M132-N132-O132-P132-Q132)</f>
       </c>
       <c r="T132" s="3">
-        <f>IF($J132="","",(S132-V132)/I132*100)</f>
+        <f>IF($J132="","",(S132-Z132)/I132*100)</f>
       </c>
       <c r="U132" s="3">
         <f>IF($J132="","",L132-R132)</f>
       </c>
-      <c r="W132" s="3">
-        <f>IF($J132="","",S132-V132)</f>
-      </c>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA132" s="3">
+        <f>IF($J132="","",S132-Z132)</f>
+      </c>
+    </row>
+    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="I133" s="3"/>
@@ -6046,16 +6070,16 @@
         <f>IF($J133="","",K133-L133-M133-N133-O133-P133-Q133)</f>
       </c>
       <c r="T133" s="3">
-        <f>IF($J133="","",(S133-V133)/I133*100)</f>
+        <f>IF($J133="","",(S133-Z133)/I133*100)</f>
       </c>
       <c r="U133" s="3">
         <f>IF($J133="","",L133-R133)</f>
       </c>
-      <c r="W133" s="3">
-        <f>IF($J133="","",S133-V133)</f>
-      </c>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA133" s="3">
+        <f>IF($J133="","",S133-Z133)</f>
+      </c>
+    </row>
+    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="I134" s="3"/>
@@ -6086,16 +6110,16 @@
         <f>IF($J134="","",K134-L134-M134-N134-O134-P134-Q134)</f>
       </c>
       <c r="T134" s="3">
-        <f>IF($J134="","",(S134-V134)/I134*100)</f>
+        <f>IF($J134="","",(S134-Z134)/I134*100)</f>
       </c>
       <c r="U134" s="3">
         <f>IF($J134="","",L134-R134)</f>
       </c>
-      <c r="W134" s="3">
-        <f>IF($J134="","",S134-V134)</f>
-      </c>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA134" s="3">
+        <f>IF($J134="","",S134-Z134)</f>
+      </c>
+    </row>
+    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="I135" s="3"/>
@@ -6126,16 +6150,16 @@
         <f>IF($J135="","",K135-L135-M135-N135-O135-P135-Q135)</f>
       </c>
       <c r="T135" s="3">
-        <f>IF($J135="","",(S135-V135)/I135*100)</f>
+        <f>IF($J135="","",(S135-Z135)/I135*100)</f>
       </c>
       <c r="U135" s="3">
         <f>IF($J135="","",L135-R135)</f>
       </c>
-      <c r="W135" s="3">
-        <f>IF($J135="","",S135-V135)</f>
-      </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA135" s="3">
+        <f>IF($J135="","",S135-Z135)</f>
+      </c>
+    </row>
+    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="I136" s="3"/>
@@ -6166,16 +6190,16 @@
         <f>IF($J136="","",K136-L136-M136-N136-O136-P136-Q136)</f>
       </c>
       <c r="T136" s="3">
-        <f>IF($J136="","",(S136-V136)/I136*100)</f>
+        <f>IF($J136="","",(S136-Z136)/I136*100)</f>
       </c>
       <c r="U136" s="3">
         <f>IF($J136="","",L136-R136)</f>
       </c>
-      <c r="W136" s="3">
-        <f>IF($J136="","",S136-V136)</f>
-      </c>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA136" s="3">
+        <f>IF($J136="","",S136-Z136)</f>
+      </c>
+    </row>
+    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="I137" s="3"/>
@@ -6206,16 +6230,16 @@
         <f>IF($J137="","",K137-L137-M137-N137-O137-P137-Q137)</f>
       </c>
       <c r="T137" s="3">
-        <f>IF($J137="","",(S137-V137)/I137*100)</f>
+        <f>IF($J137="","",(S137-Z137)/I137*100)</f>
       </c>
       <c r="U137" s="3">
         <f>IF($J137="","",L137-R137)</f>
       </c>
-      <c r="W137" s="3">
-        <f>IF($J137="","",S137-V137)</f>
-      </c>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA137" s="3">
+        <f>IF($J137="","",S137-Z137)</f>
+      </c>
+    </row>
+    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="I138" s="3"/>
@@ -6246,16 +6270,16 @@
         <f>IF($J138="","",K138-L138-M138-N138-O138-P138-Q138)</f>
       </c>
       <c r="T138" s="3">
-        <f>IF($J138="","",(S138-V138)/I138*100)</f>
+        <f>IF($J138="","",(S138-Z138)/I138*100)</f>
       </c>
       <c r="U138" s="3">
         <f>IF($J138="","",L138-R138)</f>
       </c>
-      <c r="W138" s="3">
-        <f>IF($J138="","",S138-V138)</f>
-      </c>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA138" s="3">
+        <f>IF($J138="","",S138-Z138)</f>
+      </c>
+    </row>
+    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="I139" s="3"/>
@@ -6286,16 +6310,16 @@
         <f>IF($J139="","",K139-L139-M139-N139-O139-P139-Q139)</f>
       </c>
       <c r="T139" s="3">
-        <f>IF($J139="","",(S139-V139)/I139*100)</f>
+        <f>IF($J139="","",(S139-Z139)/I139*100)</f>
       </c>
       <c r="U139" s="3">
         <f>IF($J139="","",L139-R139)</f>
       </c>
-      <c r="W139" s="3">
-        <f>IF($J139="","",S139-V139)</f>
-      </c>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA139" s="3">
+        <f>IF($J139="","",S139-Z139)</f>
+      </c>
+    </row>
+    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="I140" s="3"/>
@@ -6326,16 +6350,16 @@
         <f>IF($J140="","",K140-L140-M140-N140-O140-P140-Q140)</f>
       </c>
       <c r="T140" s="3">
-        <f>IF($J140="","",(S140-V140)/I140*100)</f>
+        <f>IF($J140="","",(S140-Z140)/I140*100)</f>
       </c>
       <c r="U140" s="3">
         <f>IF($J140="","",L140-R140)</f>
       </c>
-      <c r="W140" s="3">
-        <f>IF($J140="","",S140-V140)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA140" s="3">
+        <f>IF($J140="","",S140-Z140)</f>
+      </c>
+    </row>
+    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="I141" s="3"/>
@@ -6366,16 +6390,16 @@
         <f>IF($J141="","",K141-L141-M141-N141-O141-P141-Q141)</f>
       </c>
       <c r="T141" s="3">
-        <f>IF($J141="","",(S141-V141)/I141*100)</f>
+        <f>IF($J141="","",(S141-Z141)/I141*100)</f>
       </c>
       <c r="U141" s="3">
         <f>IF($J141="","",L141-R141)</f>
       </c>
-      <c r="W141" s="3">
-        <f>IF($J141="","",S141-V141)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA141" s="3">
+        <f>IF($J141="","",S141-Z141)</f>
+      </c>
+    </row>
+    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="I142" s="3"/>
@@ -6406,16 +6430,16 @@
         <f>IF($J142="","",K142-L142-M142-N142-O142-P142-Q142)</f>
       </c>
       <c r="T142" s="3">
-        <f>IF($J142="","",(S142-V142)/I142*100)</f>
+        <f>IF($J142="","",(S142-Z142)/I142*100)</f>
       </c>
       <c r="U142" s="3">
         <f>IF($J142="","",L142-R142)</f>
       </c>
-      <c r="W142" s="3">
-        <f>IF($J142="","",S142-V142)</f>
-      </c>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA142" s="3">
+        <f>IF($J142="","",S142-Z142)</f>
+      </c>
+    </row>
+    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="I143" s="3"/>
@@ -6446,16 +6470,16 @@
         <f>IF($J143="","",K143-L143-M143-N143-O143-P143-Q143)</f>
       </c>
       <c r="T143" s="3">
-        <f>IF($J143="","",(S143-V143)/I143*100)</f>
+        <f>IF($J143="","",(S143-Z143)/I143*100)</f>
       </c>
       <c r="U143" s="3">
         <f>IF($J143="","",L143-R143)</f>
       </c>
-      <c r="W143" s="3">
-        <f>IF($J143="","",S143-V143)</f>
-      </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA143" s="3">
+        <f>IF($J143="","",S143-Z143)</f>
+      </c>
+    </row>
+    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="I144" s="3"/>
@@ -6486,16 +6510,16 @@
         <f>IF($J144="","",K144-L144-M144-N144-O144-P144-Q144)</f>
       </c>
       <c r="T144" s="3">
-        <f>IF($J144="","",(S144-V144)/I144*100)</f>
+        <f>IF($J144="","",(S144-Z144)/I144*100)</f>
       </c>
       <c r="U144" s="3">
         <f>IF($J144="","",L144-R144)</f>
       </c>
-      <c r="W144" s="3">
-        <f>IF($J144="","",S144-V144)</f>
-      </c>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA144" s="3">
+        <f>IF($J144="","",S144-Z144)</f>
+      </c>
+    </row>
+    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="I145" s="3"/>
@@ -6526,16 +6550,16 @@
         <f>IF($J145="","",K145-L145-M145-N145-O145-P145-Q145)</f>
       </c>
       <c r="T145" s="3">
-        <f>IF($J145="","",(S145-V145)/I145*100)</f>
+        <f>IF($J145="","",(S145-Z145)/I145*100)</f>
       </c>
       <c r="U145" s="3">
         <f>IF($J145="","",L145-R145)</f>
       </c>
-      <c r="W145" s="3">
-        <f>IF($J145="","",S145-V145)</f>
-      </c>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA145" s="3">
+        <f>IF($J145="","",S145-Z145)</f>
+      </c>
+    </row>
+    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="I146" s="3"/>
@@ -6566,16 +6590,16 @@
         <f>IF($J146="","",K146-L146-M146-N146-O146-P146-Q146)</f>
       </c>
       <c r="T146" s="3">
-        <f>IF($J146="","",(S146-V146)/I146*100)</f>
+        <f>IF($J146="","",(S146-Z146)/I146*100)</f>
       </c>
       <c r="U146" s="3">
         <f>IF($J146="","",L146-R146)</f>
       </c>
-      <c r="W146" s="3">
-        <f>IF($J146="","",S146-V146)</f>
-      </c>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA146" s="3">
+        <f>IF($J146="","",S146-Z146)</f>
+      </c>
+    </row>
+    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="I147" s="3"/>
@@ -6606,16 +6630,16 @@
         <f>IF($J147="","",K147-L147-M147-N147-O147-P147-Q147)</f>
       </c>
       <c r="T147" s="3">
-        <f>IF($J147="","",(S147-V147)/I147*100)</f>
+        <f>IF($J147="","",(S147-Z147)/I147*100)</f>
       </c>
       <c r="U147" s="3">
         <f>IF($J147="","",L147-R147)</f>
       </c>
-      <c r="W147" s="3">
-        <f>IF($J147="","",S147-V147)</f>
-      </c>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA147" s="3">
+        <f>IF($J147="","",S147-Z147)</f>
+      </c>
+    </row>
+    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="I148" s="3"/>
@@ -6646,16 +6670,16 @@
         <f>IF($J148="","",K148-L148-M148-N148-O148-P148-Q148)</f>
       </c>
       <c r="T148" s="3">
-        <f>IF($J148="","",(S148-V148)/I148*100)</f>
+        <f>IF($J148="","",(S148-Z148)/I148*100)</f>
       </c>
       <c r="U148" s="3">
         <f>IF($J148="","",L148-R148)</f>
       </c>
-      <c r="W148" s="3">
-        <f>IF($J148="","",S148-V148)</f>
-      </c>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA148" s="3">
+        <f>IF($J148="","",S148-Z148)</f>
+      </c>
+    </row>
+    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="I149" s="3"/>
@@ -6686,16 +6710,16 @@
         <f>IF($J149="","",K149-L149-M149-N149-O149-P149-Q149)</f>
       </c>
       <c r="T149" s="3">
-        <f>IF($J149="","",(S149-V149)/I149*100)</f>
+        <f>IF($J149="","",(S149-Z149)/I149*100)</f>
       </c>
       <c r="U149" s="3">
         <f>IF($J149="","",L149-R149)</f>
       </c>
-      <c r="W149" s="3">
-        <f>IF($J149="","",S149-V149)</f>
-      </c>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA149" s="3">
+        <f>IF($J149="","",S149-Z149)</f>
+      </c>
+    </row>
+    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="I150" s="3"/>
@@ -6726,16 +6750,16 @@
         <f>IF($J150="","",K150-L150-M150-N150-O150-P150-Q150)</f>
       </c>
       <c r="T150" s="3">
-        <f>IF($J150="","",(S150-V150)/I150*100)</f>
+        <f>IF($J150="","",(S150-Z150)/I150*100)</f>
       </c>
       <c r="U150" s="3">
         <f>IF($J150="","",L150-R150)</f>
       </c>
-      <c r="W150" s="3">
-        <f>IF($J150="","",S150-V150)</f>
-      </c>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA150" s="3">
+        <f>IF($J150="","",S150-Z150)</f>
+      </c>
+    </row>
+    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="I151" s="3"/>
@@ -6766,16 +6790,16 @@
         <f>IF($J151="","",K151-L151-M151-N151-O151-P151-Q151)</f>
       </c>
       <c r="T151" s="3">
-        <f>IF($J151="","",(S151-V151)/I151*100)</f>
+        <f>IF($J151="","",(S151-Z151)/I151*100)</f>
       </c>
       <c r="U151" s="3">
         <f>IF($J151="","",L151-R151)</f>
       </c>
-      <c r="W151" s="3">
-        <f>IF($J151="","",S151-V151)</f>
-      </c>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA151" s="3">
+        <f>IF($J151="","",S151-Z151)</f>
+      </c>
+    </row>
+    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="I152" s="3"/>
@@ -6806,16 +6830,16 @@
         <f>IF($J152="","",K152-L152-M152-N152-O152-P152-Q152)</f>
       </c>
       <c r="T152" s="3">
-        <f>IF($J152="","",(S152-V152)/I152*100)</f>
+        <f>IF($J152="","",(S152-Z152)/I152*100)</f>
       </c>
       <c r="U152" s="3">
         <f>IF($J152="","",L152-R152)</f>
       </c>
-      <c r="W152" s="3">
-        <f>IF($J152="","",S152-V152)</f>
-      </c>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA152" s="3">
+        <f>IF($J152="","",S152-Z152)</f>
+      </c>
+    </row>
+    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="I153" s="3"/>
@@ -6846,16 +6870,16 @@
         <f>IF($J153="","",K153-L153-M153-N153-O153-P153-Q153)</f>
       </c>
       <c r="T153" s="3">
-        <f>IF($J153="","",(S153-V153)/I153*100)</f>
+        <f>IF($J153="","",(S153-Z153)/I153*100)</f>
       </c>
       <c r="U153" s="3">
         <f>IF($J153="","",L153-R153)</f>
       </c>
-      <c r="W153" s="3">
-        <f>IF($J153="","",S153-V153)</f>
-      </c>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA153" s="3">
+        <f>IF($J153="","",S153-Z153)</f>
+      </c>
+    </row>
+    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="I154" s="3"/>
@@ -6886,16 +6910,16 @@
         <f>IF($J154="","",K154-L154-M154-N154-O154-P154-Q154)</f>
       </c>
       <c r="T154" s="3">
-        <f>IF($J154="","",(S154-V154)/I154*100)</f>
+        <f>IF($J154="","",(S154-Z154)/I154*100)</f>
       </c>
       <c r="U154" s="3">
         <f>IF($J154="","",L154-R154)</f>
       </c>
-      <c r="W154" s="3">
-        <f>IF($J154="","",S154-V154)</f>
-      </c>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA154" s="3">
+        <f>IF($J154="","",S154-Z154)</f>
+      </c>
+    </row>
+    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="I155" s="3"/>
@@ -6926,16 +6950,16 @@
         <f>IF($J155="","",K155-L155-M155-N155-O155-P155-Q155)</f>
       </c>
       <c r="T155" s="3">
-        <f>IF($J155="","",(S155-V155)/I155*100)</f>
+        <f>IF($J155="","",(S155-Z155)/I155*100)</f>
       </c>
       <c r="U155" s="3">
         <f>IF($J155="","",L155-R155)</f>
       </c>
-      <c r="W155" s="3">
-        <f>IF($J155="","",S155-V155)</f>
-      </c>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA155" s="3">
+        <f>IF($J155="","",S155-Z155)</f>
+      </c>
+    </row>
+    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="I156" s="3"/>
@@ -6966,16 +6990,16 @@
         <f>IF($J156="","",K156-L156-M156-N156-O156-P156-Q156)</f>
       </c>
       <c r="T156" s="3">
-        <f>IF($J156="","",(S156-V156)/I156*100)</f>
+        <f>IF($J156="","",(S156-Z156)/I156*100)</f>
       </c>
       <c r="U156" s="3">
         <f>IF($J156="","",L156-R156)</f>
       </c>
-      <c r="W156" s="3">
-        <f>IF($J156="","",S156-V156)</f>
-      </c>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA156" s="3">
+        <f>IF($J156="","",S156-Z156)</f>
+      </c>
+    </row>
+    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="I157" s="3"/>
@@ -7006,16 +7030,16 @@
         <f>IF($J157="","",K157-L157-M157-N157-O157-P157-Q157)</f>
       </c>
       <c r="T157" s="3">
-        <f>IF($J157="","",(S157-V157)/I157*100)</f>
+        <f>IF($J157="","",(S157-Z157)/I157*100)</f>
       </c>
       <c r="U157" s="3">
         <f>IF($J157="","",L157-R157)</f>
       </c>
-      <c r="W157" s="3">
-        <f>IF($J157="","",S157-V157)</f>
-      </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA157" s="3">
+        <f>IF($J157="","",S157-Z157)</f>
+      </c>
+    </row>
+    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="I158" s="3"/>
@@ -7046,16 +7070,16 @@
         <f>IF($J158="","",K158-L158-M158-N158-O158-P158-Q158)</f>
       </c>
       <c r="T158" s="3">
-        <f>IF($J158="","",(S158-V158)/I158*100)</f>
+        <f>IF($J158="","",(S158-Z158)/I158*100)</f>
       </c>
       <c r="U158" s="3">
         <f>IF($J158="","",L158-R158)</f>
       </c>
-      <c r="W158" s="3">
-        <f>IF($J158="","",S158-V158)</f>
-      </c>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA158" s="3">
+        <f>IF($J158="","",S158-Z158)</f>
+      </c>
+    </row>
+    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="I159" s="3"/>
@@ -7086,16 +7110,16 @@
         <f>IF($J159="","",K159-L159-M159-N159-O159-P159-Q159)</f>
       </c>
       <c r="T159" s="3">
-        <f>IF($J159="","",(S159-V159)/I159*100)</f>
+        <f>IF($J159="","",(S159-Z159)/I159*100)</f>
       </c>
       <c r="U159" s="3">
         <f>IF($J159="","",L159-R159)</f>
       </c>
-      <c r="W159" s="3">
-        <f>IF($J159="","",S159-V159)</f>
-      </c>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA159" s="3">
+        <f>IF($J159="","",S159-Z159)</f>
+      </c>
+    </row>
+    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="I160" s="3"/>
@@ -7126,16 +7150,16 @@
         <f>IF($J160="","",K160-L160-M160-N160-O160-P160-Q160)</f>
       </c>
       <c r="T160" s="3">
-        <f>IF($J160="","",(S160-V160)/I160*100)</f>
+        <f>IF($J160="","",(S160-Z160)/I160*100)</f>
       </c>
       <c r="U160" s="3">
         <f>IF($J160="","",L160-R160)</f>
       </c>
-      <c r="W160" s="3">
-        <f>IF($J160="","",S160-V160)</f>
-      </c>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA160" s="3">
+        <f>IF($J160="","",S160-Z160)</f>
+      </c>
+    </row>
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="I161" s="3"/>
@@ -7166,16 +7190,16 @@
         <f>IF($J161="","",K161-L161-M161-N161-O161-P161-Q161)</f>
       </c>
       <c r="T161" s="3">
-        <f>IF($J161="","",(S161-V161)/I161*100)</f>
+        <f>IF($J161="","",(S161-Z161)/I161*100)</f>
       </c>
       <c r="U161" s="3">
         <f>IF($J161="","",L161-R161)</f>
       </c>
-      <c r="W161" s="3">
-        <f>IF($J161="","",S161-V161)</f>
-      </c>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA161" s="3">
+        <f>IF($J161="","",S161-Z161)</f>
+      </c>
+    </row>
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="I162" s="3"/>
@@ -7206,16 +7230,16 @@
         <f>IF($J162="","",K162-L162-M162-N162-O162-P162-Q162)</f>
       </c>
       <c r="T162" s="3">
-        <f>IF($J162="","",(S162-V162)/I162*100)</f>
+        <f>IF($J162="","",(S162-Z162)/I162*100)</f>
       </c>
       <c r="U162" s="3">
         <f>IF($J162="","",L162-R162)</f>
       </c>
-      <c r="W162" s="3">
-        <f>IF($J162="","",S162-V162)</f>
-      </c>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA162" s="3">
+        <f>IF($J162="","",S162-Z162)</f>
+      </c>
+    </row>
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="I163" s="3"/>
@@ -7246,16 +7270,16 @@
         <f>IF($J163="","",K163-L163-M163-N163-O163-P163-Q163)</f>
       </c>
       <c r="T163" s="3">
-        <f>IF($J163="","",(S163-V163)/I163*100)</f>
+        <f>IF($J163="","",(S163-Z163)/I163*100)</f>
       </c>
       <c r="U163" s="3">
         <f>IF($J163="","",L163-R163)</f>
       </c>
-      <c r="W163" s="3">
-        <f>IF($J163="","",S163-V163)</f>
-      </c>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA163" s="3">
+        <f>IF($J163="","",S163-Z163)</f>
+      </c>
+    </row>
+    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="I164" s="3"/>
@@ -7286,16 +7310,16 @@
         <f>IF($J164="","",K164-L164-M164-N164-O164-P164-Q164)</f>
       </c>
       <c r="T164" s="3">
-        <f>IF($J164="","",(S164-V164)/I164*100)</f>
+        <f>IF($J164="","",(S164-Z164)/I164*100)</f>
       </c>
       <c r="U164" s="3">
         <f>IF($J164="","",L164-R164)</f>
       </c>
-      <c r="W164" s="3">
-        <f>IF($J164="","",S164-V164)</f>
-      </c>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA164" s="3">
+        <f>IF($J164="","",S164-Z164)</f>
+      </c>
+    </row>
+    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="I165" s="3"/>
@@ -7326,16 +7350,16 @@
         <f>IF($J165="","",K165-L165-M165-N165-O165-P165-Q165)</f>
       </c>
       <c r="T165" s="3">
-        <f>IF($J165="","",(S165-V165)/I165*100)</f>
+        <f>IF($J165="","",(S165-Z165)/I165*100)</f>
       </c>
       <c r="U165" s="3">
         <f>IF($J165="","",L165-R165)</f>
       </c>
-      <c r="W165" s="3">
-        <f>IF($J165="","",S165-V165)</f>
-      </c>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA165" s="3">
+        <f>IF($J165="","",S165-Z165)</f>
+      </c>
+    </row>
+    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="I166" s="3"/>
@@ -7366,16 +7390,16 @@
         <f>IF($J166="","",K166-L166-M166-N166-O166-P166-Q166)</f>
       </c>
       <c r="T166" s="3">
-        <f>IF($J166="","",(S166-V166)/I166*100)</f>
+        <f>IF($J166="","",(S166-Z166)/I166*100)</f>
       </c>
       <c r="U166" s="3">
         <f>IF($J166="","",L166-R166)</f>
       </c>
-      <c r="W166" s="3">
-        <f>IF($J166="","",S166-V166)</f>
-      </c>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA166" s="3">
+        <f>IF($J166="","",S166-Z166)</f>
+      </c>
+    </row>
+    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="I167" s="3"/>
@@ -7406,16 +7430,16 @@
         <f>IF($J167="","",K167-L167-M167-N167-O167-P167-Q167)</f>
       </c>
       <c r="T167" s="3">
-        <f>IF($J167="","",(S167-V167)/I167*100)</f>
+        <f>IF($J167="","",(S167-Z167)/I167*100)</f>
       </c>
       <c r="U167" s="3">
         <f>IF($J167="","",L167-R167)</f>
       </c>
-      <c r="W167" s="3">
-        <f>IF($J167="","",S167-V167)</f>
-      </c>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA167" s="3">
+        <f>IF($J167="","",S167-Z167)</f>
+      </c>
+    </row>
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="I168" s="3"/>
@@ -7446,16 +7470,16 @@
         <f>IF($J168="","",K168-L168-M168-N168-O168-P168-Q168)</f>
       </c>
       <c r="T168" s="3">
-        <f>IF($J168="","",(S168-V168)/I168*100)</f>
+        <f>IF($J168="","",(S168-Z168)/I168*100)</f>
       </c>
       <c r="U168" s="3">
         <f>IF($J168="","",L168-R168)</f>
       </c>
-      <c r="W168" s="3">
-        <f>IF($J168="","",S168-V168)</f>
-      </c>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA168" s="3">
+        <f>IF($J168="","",S168-Z168)</f>
+      </c>
+    </row>
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="I169" s="3"/>
@@ -7486,16 +7510,16 @@
         <f>IF($J169="","",K169-L169-M169-N169-O169-P169-Q169)</f>
       </c>
       <c r="T169" s="3">
-        <f>IF($J169="","",(S169-V169)/I169*100)</f>
+        <f>IF($J169="","",(S169-Z169)/I169*100)</f>
       </c>
       <c r="U169" s="3">
         <f>IF($J169="","",L169-R169)</f>
       </c>
-      <c r="W169" s="3">
-        <f>IF($J169="","",S169-V169)</f>
-      </c>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA169" s="3">
+        <f>IF($J169="","",S169-Z169)</f>
+      </c>
+    </row>
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="I170" s="3"/>
@@ -7526,16 +7550,16 @@
         <f>IF($J170="","",K170-L170-M170-N170-O170-P170-Q170)</f>
       </c>
       <c r="T170" s="3">
-        <f>IF($J170="","",(S170-V170)/I170*100)</f>
+        <f>IF($J170="","",(S170-Z170)/I170*100)</f>
       </c>
       <c r="U170" s="3">
         <f>IF($J170="","",L170-R170)</f>
       </c>
-      <c r="W170" s="3">
-        <f>IF($J170="","",S170-V170)</f>
-      </c>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA170" s="3">
+        <f>IF($J170="","",S170-Z170)</f>
+      </c>
+    </row>
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="I171" s="3"/>
@@ -7566,16 +7590,16 @@
         <f>IF($J171="","",K171-L171-M171-N171-O171-P171-Q171)</f>
       </c>
       <c r="T171" s="3">
-        <f>IF($J171="","",(S171-V171)/I171*100)</f>
+        <f>IF($J171="","",(S171-Z171)/I171*100)</f>
       </c>
       <c r="U171" s="3">
         <f>IF($J171="","",L171-R171)</f>
       </c>
-      <c r="W171" s="3">
-        <f>IF($J171="","",S171-V171)</f>
-      </c>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA171" s="3">
+        <f>IF($J171="","",S171-Z171)</f>
+      </c>
+    </row>
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="I172" s="3"/>
@@ -7606,16 +7630,16 @@
         <f>IF($J172="","",K172-L172-M172-N172-O172-P172-Q172)</f>
       </c>
       <c r="T172" s="3">
-        <f>IF($J172="","",(S172-V172)/I172*100)</f>
+        <f>IF($J172="","",(S172-Z172)/I172*100)</f>
       </c>
       <c r="U172" s="3">
         <f>IF($J172="","",L172-R172)</f>
       </c>
-      <c r="W172" s="3">
-        <f>IF($J172="","",S172-V172)</f>
-      </c>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA172" s="3">
+        <f>IF($J172="","",S172-Z172)</f>
+      </c>
+    </row>
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="I173" s="3"/>
@@ -7646,16 +7670,16 @@
         <f>IF($J173="","",K173-L173-M173-N173-O173-P173-Q173)</f>
       </c>
       <c r="T173" s="3">
-        <f>IF($J173="","",(S173-V173)/I173*100)</f>
+        <f>IF($J173="","",(S173-Z173)/I173*100)</f>
       </c>
       <c r="U173" s="3">
         <f>IF($J173="","",L173-R173)</f>
       </c>
-      <c r="W173" s="3">
-        <f>IF($J173="","",S173-V173)</f>
-      </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA173" s="3">
+        <f>IF($J173="","",S173-Z173)</f>
+      </c>
+    </row>
+    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="I174" s="3"/>
@@ -7686,16 +7710,16 @@
         <f>IF($J174="","",K174-L174-M174-N174-O174-P174-Q174)</f>
       </c>
       <c r="T174" s="3">
-        <f>IF($J174="","",(S174-V174)/I174*100)</f>
+        <f>IF($J174="","",(S174-Z174)/I174*100)</f>
       </c>
       <c r="U174" s="3">
         <f>IF($J174="","",L174-R174)</f>
       </c>
-      <c r="W174" s="3">
-        <f>IF($J174="","",S174-V174)</f>
-      </c>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA174" s="3">
+        <f>IF($J174="","",S174-Z174)</f>
+      </c>
+    </row>
+    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="I175" s="3"/>
@@ -7726,16 +7750,16 @@
         <f>IF($J175="","",K175-L175-M175-N175-O175-P175-Q175)</f>
       </c>
       <c r="T175" s="3">
-        <f>IF($J175="","",(S175-V175)/I175*100)</f>
+        <f>IF($J175="","",(S175-Z175)/I175*100)</f>
       </c>
       <c r="U175" s="3">
         <f>IF($J175="","",L175-R175)</f>
       </c>
-      <c r="W175" s="3">
-        <f>IF($J175="","",S175-V175)</f>
-      </c>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA175" s="3">
+        <f>IF($J175="","",S175-Z175)</f>
+      </c>
+    </row>
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="I176" s="3"/>
@@ -7766,16 +7790,16 @@
         <f>IF($J176="","",K176-L176-M176-N176-O176-P176-Q176)</f>
       </c>
       <c r="T176" s="3">
-        <f>IF($J176="","",(S176-V176)/I176*100)</f>
+        <f>IF($J176="","",(S176-Z176)/I176*100)</f>
       </c>
       <c r="U176" s="3">
         <f>IF($J176="","",L176-R176)</f>
       </c>
-      <c r="W176" s="3">
-        <f>IF($J176="","",S176-V176)</f>
-      </c>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA176" s="3">
+        <f>IF($J176="","",S176-Z176)</f>
+      </c>
+    </row>
+    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="I177" s="3"/>
@@ -7806,16 +7830,16 @@
         <f>IF($J177="","",K177-L177-M177-N177-O177-P177-Q177)</f>
       </c>
       <c r="T177" s="3">
-        <f>IF($J177="","",(S177-V177)/I177*100)</f>
+        <f>IF($J177="","",(S177-Z177)/I177*100)</f>
       </c>
       <c r="U177" s="3">
         <f>IF($J177="","",L177-R177)</f>
       </c>
-      <c r="W177" s="3">
-        <f>IF($J177="","",S177-V177)</f>
-      </c>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA177" s="3">
+        <f>IF($J177="","",S177-Z177)</f>
+      </c>
+    </row>
+    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="I178" s="3"/>
@@ -7846,16 +7870,16 @@
         <f>IF($J178="","",K178-L178-M178-N178-O178-P178-Q178)</f>
       </c>
       <c r="T178" s="3">
-        <f>IF($J178="","",(S178-V178)/I178*100)</f>
+        <f>IF($J178="","",(S178-Z178)/I178*100)</f>
       </c>
       <c r="U178" s="3">
         <f>IF($J178="","",L178-R178)</f>
       </c>
-      <c r="W178" s="3">
-        <f>IF($J178="","",S178-V178)</f>
-      </c>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA178" s="3">
+        <f>IF($J178="","",S178-Z178)</f>
+      </c>
+    </row>
+    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="I179" s="3"/>
@@ -7886,16 +7910,16 @@
         <f>IF($J179="","",K179-L179-M179-N179-O179-P179-Q179)</f>
       </c>
       <c r="T179" s="3">
-        <f>IF($J179="","",(S179-V179)/I179*100)</f>
+        <f>IF($J179="","",(S179-Z179)/I179*100)</f>
       </c>
       <c r="U179" s="3">
         <f>IF($J179="","",L179-R179)</f>
       </c>
-      <c r="W179" s="3">
-        <f>IF($J179="","",S179-V179)</f>
-      </c>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA179" s="3">
+        <f>IF($J179="","",S179-Z179)</f>
+      </c>
+    </row>
+    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="I180" s="3"/>
@@ -7926,16 +7950,16 @@
         <f>IF($J180="","",K180-L180-M180-N180-O180-P180-Q180)</f>
       </c>
       <c r="T180" s="3">
-        <f>IF($J180="","",(S180-V180)/I180*100)</f>
+        <f>IF($J180="","",(S180-Z180)/I180*100)</f>
       </c>
       <c r="U180" s="3">
         <f>IF($J180="","",L180-R180)</f>
       </c>
-      <c r="W180" s="3">
-        <f>IF($J180="","",S180-V180)</f>
-      </c>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA180" s="3">
+        <f>IF($J180="","",S180-Z180)</f>
+      </c>
+    </row>
+    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="I181" s="3"/>
@@ -7966,16 +7990,16 @@
         <f>IF($J181="","",K181-L181-M181-N181-O181-P181-Q181)</f>
       </c>
       <c r="T181" s="3">
-        <f>IF($J181="","",(S181-V181)/I181*100)</f>
+        <f>IF($J181="","",(S181-Z181)/I181*100)</f>
       </c>
       <c r="U181" s="3">
         <f>IF($J181="","",L181-R181)</f>
       </c>
-      <c r="W181" s="3">
-        <f>IF($J181="","",S181-V181)</f>
-      </c>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA181" s="3">
+        <f>IF($J181="","",S181-Z181)</f>
+      </c>
+    </row>
+    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="I182" s="3"/>
@@ -8006,16 +8030,16 @@
         <f>IF($J182="","",K182-L182-M182-N182-O182-P182-Q182)</f>
       </c>
       <c r="T182" s="3">
-        <f>IF($J182="","",(S182-V182)/I182*100)</f>
+        <f>IF($J182="","",(S182-Z182)/I182*100)</f>
       </c>
       <c r="U182" s="3">
         <f>IF($J182="","",L182-R182)</f>
       </c>
-      <c r="W182" s="3">
-        <f>IF($J182="","",S182-V182)</f>
-      </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA182" s="3">
+        <f>IF($J182="","",S182-Z182)</f>
+      </c>
+    </row>
+    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="I183" s="3"/>
@@ -8046,16 +8070,16 @@
         <f>IF($J183="","",K183-L183-M183-N183-O183-P183-Q183)</f>
       </c>
       <c r="T183" s="3">
-        <f>IF($J183="","",(S183-V183)/I183*100)</f>
+        <f>IF($J183="","",(S183-Z183)/I183*100)</f>
       </c>
       <c r="U183" s="3">
         <f>IF($J183="","",L183-R183)</f>
       </c>
-      <c r="W183" s="3">
-        <f>IF($J183="","",S183-V183)</f>
-      </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA183" s="3">
+        <f>IF($J183="","",S183-Z183)</f>
+      </c>
+    </row>
+    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="I184" s="3"/>
@@ -8086,16 +8110,16 @@
         <f>IF($J184="","",K184-L184-M184-N184-O184-P184-Q184)</f>
       </c>
       <c r="T184" s="3">
-        <f>IF($J184="","",(S184-V184)/I184*100)</f>
+        <f>IF($J184="","",(S184-Z184)/I184*100)</f>
       </c>
       <c r="U184" s="3">
         <f>IF($J184="","",L184-R184)</f>
       </c>
-      <c r="W184" s="3">
-        <f>IF($J184="","",S184-V184)</f>
-      </c>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA184" s="3">
+        <f>IF($J184="","",S184-Z184)</f>
+      </c>
+    </row>
+    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="I185" s="3"/>
@@ -8126,16 +8150,16 @@
         <f>IF($J185="","",K185-L185-M185-N185-O185-P185-Q185)</f>
       </c>
       <c r="T185" s="3">
-        <f>IF($J185="","",(S185-V185)/I185*100)</f>
+        <f>IF($J185="","",(S185-Z185)/I185*100)</f>
       </c>
       <c r="U185" s="3">
         <f>IF($J185="","",L185-R185)</f>
       </c>
-      <c r="W185" s="3">
-        <f>IF($J185="","",S185-V185)</f>
-      </c>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA185" s="3">
+        <f>IF($J185="","",S185-Z185)</f>
+      </c>
+    </row>
+    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="I186" s="3"/>
@@ -8166,16 +8190,16 @@
         <f>IF($J186="","",K186-L186-M186-N186-O186-P186-Q186)</f>
       </c>
       <c r="T186" s="3">
-        <f>IF($J186="","",(S186-V186)/I186*100)</f>
+        <f>IF($J186="","",(S186-Z186)/I186*100)</f>
       </c>
       <c r="U186" s="3">
         <f>IF($J186="","",L186-R186)</f>
       </c>
-      <c r="W186" s="3">
-        <f>IF($J186="","",S186-V186)</f>
-      </c>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA186" s="3">
+        <f>IF($J186="","",S186-Z186)</f>
+      </c>
+    </row>
+    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="I187" s="3"/>
@@ -8206,16 +8230,16 @@
         <f>IF($J187="","",K187-L187-M187-N187-O187-P187-Q187)</f>
       </c>
       <c r="T187" s="3">
-        <f>IF($J187="","",(S187-V187)/I187*100)</f>
+        <f>IF($J187="","",(S187-Z187)/I187*100)</f>
       </c>
       <c r="U187" s="3">
         <f>IF($J187="","",L187-R187)</f>
       </c>
-      <c r="W187" s="3">
-        <f>IF($J187="","",S187-V187)</f>
-      </c>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA187" s="3">
+        <f>IF($J187="","",S187-Z187)</f>
+      </c>
+    </row>
+    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="I188" s="3"/>
@@ -8246,16 +8270,16 @@
         <f>IF($J188="","",K188-L188-M188-N188-O188-P188-Q188)</f>
       </c>
       <c r="T188" s="3">
-        <f>IF($J188="","",(S188-V188)/I188*100)</f>
+        <f>IF($J188="","",(S188-Z188)/I188*100)</f>
       </c>
       <c r="U188" s="3">
         <f>IF($J188="","",L188-R188)</f>
       </c>
-      <c r="W188" s="3">
-        <f>IF($J188="","",S188-V188)</f>
-      </c>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA188" s="3">
+        <f>IF($J188="","",S188-Z188)</f>
+      </c>
+    </row>
+    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="I189" s="3"/>
@@ -8286,16 +8310,16 @@
         <f>IF($J189="","",K189-L189-M189-N189-O189-P189-Q189)</f>
       </c>
       <c r="T189" s="3">
-        <f>IF($J189="","",(S189-V189)/I189*100)</f>
+        <f>IF($J189="","",(S189-Z189)/I189*100)</f>
       </c>
       <c r="U189" s="3">
         <f>IF($J189="","",L189-R189)</f>
       </c>
-      <c r="W189" s="3">
-        <f>IF($J189="","",S189-V189)</f>
-      </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA189" s="3">
+        <f>IF($J189="","",S189-Z189)</f>
+      </c>
+    </row>
+    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="I190" s="3"/>
@@ -8326,16 +8350,16 @@
         <f>IF($J190="","",K190-L190-M190-N190-O190-P190-Q190)</f>
       </c>
       <c r="T190" s="3">
-        <f>IF($J190="","",(S190-V190)/I190*100)</f>
+        <f>IF($J190="","",(S190-Z190)/I190*100)</f>
       </c>
       <c r="U190" s="3">
         <f>IF($J190="","",L190-R190)</f>
       </c>
-      <c r="W190" s="3">
-        <f>IF($J190="","",S190-V190)</f>
-      </c>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA190" s="3">
+        <f>IF($J190="","",S190-Z190)</f>
+      </c>
+    </row>
+    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="I191" s="3"/>
@@ -8366,16 +8390,16 @@
         <f>IF($J191="","",K191-L191-M191-N191-O191-P191-Q191)</f>
       </c>
       <c r="T191" s="3">
-        <f>IF($J191="","",(S191-V191)/I191*100)</f>
+        <f>IF($J191="","",(S191-Z191)/I191*100)</f>
       </c>
       <c r="U191" s="3">
         <f>IF($J191="","",L191-R191)</f>
       </c>
-      <c r="W191" s="3">
-        <f>IF($J191="","",S191-V191)</f>
-      </c>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA191" s="3">
+        <f>IF($J191="","",S191-Z191)</f>
+      </c>
+    </row>
+    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="I192" s="3"/>
@@ -8406,16 +8430,16 @@
         <f>IF($J192="","",K192-L192-M192-N192-O192-P192-Q192)</f>
       </c>
       <c r="T192" s="3">
-        <f>IF($J192="","",(S192-V192)/I192*100)</f>
+        <f>IF($J192="","",(S192-Z192)/I192*100)</f>
       </c>
       <c r="U192" s="3">
         <f>IF($J192="","",L192-R192)</f>
       </c>
-      <c r="W192" s="3">
-        <f>IF($J192="","",S192-V192)</f>
-      </c>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA192" s="3">
+        <f>IF($J192="","",S192-Z192)</f>
+      </c>
+    </row>
+    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="I193" s="3"/>
@@ -8446,16 +8470,16 @@
         <f>IF($J193="","",K193-L193-M193-N193-O193-P193-Q193)</f>
       </c>
       <c r="T193" s="3">
-        <f>IF($J193="","",(S193-V193)/I193*100)</f>
+        <f>IF($J193="","",(S193-Z193)/I193*100)</f>
       </c>
       <c r="U193" s="3">
         <f>IF($J193="","",L193-R193)</f>
       </c>
-      <c r="W193" s="3">
-        <f>IF($J193="","",S193-V193)</f>
-      </c>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA193" s="3">
+        <f>IF($J193="","",S193-Z193)</f>
+      </c>
+    </row>
+    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="I194" s="3"/>
@@ -8486,16 +8510,16 @@
         <f>IF($J194="","",K194-L194-M194-N194-O194-P194-Q194)</f>
       </c>
       <c r="T194" s="3">
-        <f>IF($J194="","",(S194-V194)/I194*100)</f>
+        <f>IF($J194="","",(S194-Z194)/I194*100)</f>
       </c>
       <c r="U194" s="3">
         <f>IF($J194="","",L194-R194)</f>
       </c>
-      <c r="W194" s="3">
-        <f>IF($J194="","",S194-V194)</f>
-      </c>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA194" s="3">
+        <f>IF($J194="","",S194-Z194)</f>
+      </c>
+    </row>
+    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="I195" s="3"/>
@@ -8526,16 +8550,16 @@
         <f>IF($J195="","",K195-L195-M195-N195-O195-P195-Q195)</f>
       </c>
       <c r="T195" s="3">
-        <f>IF($J195="","",(S195-V195)/I195*100)</f>
+        <f>IF($J195="","",(S195-Z195)/I195*100)</f>
       </c>
       <c r="U195" s="3">
         <f>IF($J195="","",L195-R195)</f>
       </c>
-      <c r="W195" s="3">
-        <f>IF($J195="","",S195-V195)</f>
-      </c>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA195" s="3">
+        <f>IF($J195="","",S195-Z195)</f>
+      </c>
+    </row>
+    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="I196" s="3"/>
@@ -8566,16 +8590,16 @@
         <f>IF($J196="","",K196-L196-M196-N196-O196-P196-Q196)</f>
       </c>
       <c r="T196" s="3">
-        <f>IF($J196="","",(S196-V196)/I196*100)</f>
+        <f>IF($J196="","",(S196-Z196)/I196*100)</f>
       </c>
       <c r="U196" s="3">
         <f>IF($J196="","",L196-R196)</f>
       </c>
-      <c r="W196" s="3">
-        <f>IF($J196="","",S196-V196)</f>
-      </c>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA196" s="3">
+        <f>IF($J196="","",S196-Z196)</f>
+      </c>
+    </row>
+    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="I197" s="3"/>
@@ -8606,16 +8630,16 @@
         <f>IF($J197="","",K197-L197-M197-N197-O197-P197-Q197)</f>
       </c>
       <c r="T197" s="3">
-        <f>IF($J197="","",(S197-V197)/I197*100)</f>
+        <f>IF($J197="","",(S197-Z197)/I197*100)</f>
       </c>
       <c r="U197" s="3">
         <f>IF($J197="","",L197-R197)</f>
       </c>
-      <c r="W197" s="3">
-        <f>IF($J197="","",S197-V197)</f>
-      </c>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA197" s="3">
+        <f>IF($J197="","",S197-Z197)</f>
+      </c>
+    </row>
+    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="I198" s="3"/>
@@ -8646,16 +8670,16 @@
         <f>IF($J198="","",K198-L198-M198-N198-O198-P198-Q198)</f>
       </c>
       <c r="T198" s="3">
-        <f>IF($J198="","",(S198-V198)/I198*100)</f>
+        <f>IF($J198="","",(S198-Z198)/I198*100)</f>
       </c>
       <c r="U198" s="3">
         <f>IF($J198="","",L198-R198)</f>
       </c>
-      <c r="W198" s="3">
-        <f>IF($J198="","",S198-V198)</f>
-      </c>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA198" s="3">
+        <f>IF($J198="","",S198-Z198)</f>
+      </c>
+    </row>
+    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="I199" s="3"/>
@@ -8686,16 +8710,16 @@
         <f>IF($J199="","",K199-L199-M199-N199-O199-P199-Q199)</f>
       </c>
       <c r="T199" s="3">
-        <f>IF($J199="","",(S199-V199)/I199*100)</f>
+        <f>IF($J199="","",(S199-Z199)/I199*100)</f>
       </c>
       <c r="U199" s="3">
         <f>IF($J199="","",L199-R199)</f>
       </c>
-      <c r="W199" s="3">
-        <f>IF($J199="","",S199-V199)</f>
-      </c>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA199" s="3">
+        <f>IF($J199="","",S199-Z199)</f>
+      </c>
+    </row>
+    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="I200" s="3"/>
@@ -8726,16 +8750,16 @@
         <f>IF($J200="","",K200-L200-M200-N200-O200-P200-Q200)</f>
       </c>
       <c r="T200" s="3">
-        <f>IF($J200="","",(S200-V200)/I200*100)</f>
+        <f>IF($J200="","",(S200-Z200)/I200*100)</f>
       </c>
       <c r="U200" s="3">
         <f>IF($J200="","",L200-R200)</f>
       </c>
-      <c r="W200" s="3">
-        <f>IF($J200="","",S200-V200)</f>
-      </c>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA200" s="3">
+        <f>IF($J200="","",S200-Z200)</f>
+      </c>
+    </row>
+    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="I201" s="3"/>
@@ -8766,16 +8790,16 @@
         <f>IF($J201="","",K201-L201-M201-N201-O201-P201-Q201)</f>
       </c>
       <c r="T201" s="3">
-        <f>IF($J201="","",(S201-V201)/I201*100)</f>
+        <f>IF($J201="","",(S201-Z201)/I201*100)</f>
       </c>
       <c r="U201" s="3">
         <f>IF($J201="","",L201-R201)</f>
       </c>
-      <c r="W201" s="3">
-        <f>IF($J201="","",S201-V201)</f>
-      </c>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="AA201" s="3">
+        <f>IF($J201="","",S201-Z201)</f>
+      </c>
+    </row>
+    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="I202" s="3"/>
@@ -8806,18 +8830,18 @@
         <f>IF($J202="","",K202-L202-M202-N202-O202-P202-Q202)</f>
       </c>
       <c r="T202" s="3">
-        <f>IF($J202="","",(S202-V202)/I202*100)</f>
+        <f>IF($J202="","",(S202-Z202)/I202*100)</f>
       </c>
       <c r="U202" s="3">
         <f>IF($J202="","",L202-R202)</f>
       </c>
-      <c r="W202" s="3">
-        <f>IF($J202="","",S202-V202)</f>
-      </c>
-    </row>
-    <row r="203" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA202" s="3">
+        <f>IF($J202="","",S202-Z202)</f>
+      </c>
+    </row>
+    <row r="203" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -8860,7 +8884,7 @@
         <f>SUM(S2:S202)</f>
       </c>
       <c r="T203" s="6">
-        <f>IFERROR((S203-V203)/I203*100,0)</f>
+        <f>IFERROR((S203-Z203)/I203*100,0)</f>
       </c>
       <c r="U203" s="6">
         <f>SUM(U2:U202)</f>
@@ -8871,11 +8895,23 @@
       <c r="W203" s="6">
         <f>SUM(W2:W202)</f>
       </c>
-      <c r="X203" s="4"/>
-      <c r="Y203" s="4"/>
-      <c r="Z203" s="4"/>
-      <c r="AA203" s="4"/>
+      <c r="X203" s="6">
+        <f>SUM(X2:X202)</f>
+      </c>
+      <c r="Y203" s="6">
+        <f>SUM(Y2:Y202)</f>
+      </c>
+      <c r="Z203" s="6">
+        <f>SUM(Z2:Z202)</f>
+      </c>
+      <c r="AA203" s="6">
+        <f>SUM(AA2:AA202)</f>
+      </c>
       <c r="AB203" s="4"/>
+      <c r="AC203" s="4"/>
+      <c r="AD203" s="4"/>
+      <c r="AE203" s="4"/>
+      <c r="AF203" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
